--- a/inst/extdata/ute_mountain_ute_tribe_criteria_crosswalk.xlsx
+++ b/inst/extdata/ute_mountain_ute_tribe_criteria_crosswalk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/k_salkgundersen_tetratech_com/Documents/EPA/R8_AssessmentTool/5_Work/Crosswalks/individual_criteria_crosswalks/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwong01\TADACommunityHub\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{83638666-7EC0-46A3-8442-E0FC462EFBDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50F5F14F-865B-4854-927D-C8A959F1A688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0939A520-3B6D-499A-B5C0-4CEBC761A507}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0939A520-3B6D-499A-B5C0-4CEBC761A507}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1909" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1917" uniqueCount="173">
   <si>
     <t>TADA.ComparableDataIdentifier</t>
   </si>
@@ -275,9 +275,6 @@
     <t>arithmetic max</t>
   </si>
   <si>
-    <t>Oxygen</t>
-  </si>
-  <si>
     <t>DISSOLVED OXYGEN (DO)</t>
   </si>
   <si>
@@ -302,9 +299,6 @@
     <t>arithmetic mean min</t>
   </si>
   <si>
-    <t>E. coli</t>
-  </si>
-  <si>
     <t>ESCHERICHIA COLI</t>
   </si>
   <si>
@@ -383,9 +377,6 @@
     <t>0.10(0.29[CI-]+0.53) mg/L NO2-N; [CI-] = chloride ion concentration, upper CI- limit = 22 mg/L</t>
   </si>
   <si>
-    <t>Nitrate + Nitrite</t>
-  </si>
-  <si>
     <t>Cyanide</t>
   </si>
   <si>
@@ -458,9 +449,6 @@
     <t>e^(0.7409[In(hardness)]-4.719)*(1.101672-[(In harness)(.041838)]</t>
   </si>
   <si>
-    <t>Chromium (III)</t>
-  </si>
-  <si>
     <t>CHROMIUM(III)</t>
   </si>
   <si>
@@ -470,9 +458,6 @@
     <t>e^(0.819*Ln(hardness)+0.6848)(0.860)</t>
   </si>
   <si>
-    <t>Chromium (VI)</t>
-  </si>
-  <si>
     <t>CHROMIUM(VI)</t>
   </si>
   <si>
@@ -552,6 +537,24 @@
   </si>
   <si>
     <t>URANIUM</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>DISSOLVED OXYGEN</t>
+  </si>
+  <si>
+    <t>ESCHERICHIA COLI (E. COLI)</t>
+  </si>
+  <si>
+    <t>NITRATE/NITRITE (NITRITE + NITRATE AS N)</t>
+  </si>
+  <si>
+    <t>CHROMIUM, TRIVALENT, TOTAL</t>
+  </si>
+  <si>
+    <t>CHROMIUM, HEXAVALENT</t>
   </si>
 </sst>
 </file>
@@ -961,9 +964,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5669769F-2254-4C2D-A5BA-32D6C5B999AC}">
   <dimension ref="A1:AQ149"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="29.90625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:43" s="4" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43" s="4" customFormat="1" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1094,7 +1100,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="5"/>
       <c r="B2" s="5" t="s">
         <v>43</v>
@@ -1165,7 +1171,7 @@
       <c r="AL2" s="5"/>
       <c r="AM2" s="5"/>
     </row>
-    <row r="3" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="5"/>
       <c r="B3" s="5" t="s">
         <v>43</v>
@@ -1236,7 +1242,7 @@
       <c r="AL3" s="5"/>
       <c r="AM3" s="5"/>
     </row>
-    <row r="4" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="5"/>
       <c r="B4" s="5" t="s">
         <v>43</v>
@@ -1305,7 +1311,7 @@
       <c r="AL4" s="5"/>
       <c r="AM4" s="5"/>
     </row>
-    <row r="5" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="5"/>
       <c r="B5" s="5" t="s">
         <v>43</v>
@@ -1374,7 +1380,7 @@
       <c r="AL5" s="5"/>
       <c r="AM5" s="5"/>
     </row>
-    <row r="6" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="5"/>
       <c r="B6" s="5" t="s">
         <v>43</v>
@@ -1443,12 +1449,14 @@
       <c r="AL6" s="5"/>
       <c r="AM6" s="5"/>
     </row>
-    <row r="7" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="5"/>
       <c r="B7" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="5"/>
+      <c r="C7" s="5" t="s">
+        <v>44</v>
+      </c>
       <c r="D7" s="5" t="s">
         <v>58</v>
       </c>
@@ -1510,12 +1518,14 @@
       <c r="AL7" s="5"/>
       <c r="AM7" s="5"/>
     </row>
-    <row r="8" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="5"/>
       <c r="B8" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="5"/>
+      <c r="C8" s="5" t="s">
+        <v>167</v>
+      </c>
       <c r="D8" s="5" t="s">
         <v>58</v>
       </c>
@@ -1577,12 +1587,14 @@
       <c r="AL8" s="5"/>
       <c r="AM8" s="5"/>
     </row>
-    <row r="9" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="5"/>
       <c r="B9" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="5"/>
+      <c r="C9" s="5" t="s">
+        <v>167</v>
+      </c>
       <c r="D9" s="5" t="s">
         <v>58</v>
       </c>
@@ -1646,12 +1658,14 @@
       <c r="AL9" s="5"/>
       <c r="AM9" s="5"/>
     </row>
-    <row r="10" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="5"/>
       <c r="B10" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="5"/>
+      <c r="C10" s="5" t="s">
+        <v>167</v>
+      </c>
       <c r="D10" s="5" t="s">
         <v>58</v>
       </c>
@@ -1713,12 +1727,14 @@
       <c r="AL10" s="5"/>
       <c r="AM10" s="5"/>
     </row>
-    <row r="11" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="5"/>
       <c r="B11" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="5"/>
+      <c r="C11" s="5" t="s">
+        <v>167</v>
+      </c>
       <c r="D11" s="5" t="s">
         <v>58</v>
       </c>
@@ -1780,12 +1796,14 @@
       <c r="AL11" s="5"/>
       <c r="AM11" s="5"/>
     </row>
-    <row r="12" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="5"/>
       <c r="B12" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="5"/>
+      <c r="C12" s="5" t="s">
+        <v>113</v>
+      </c>
       <c r="D12" s="5" t="s">
         <v>58</v>
       </c>
@@ -1847,12 +1865,14 @@
       <c r="AL12" s="5"/>
       <c r="AM12" s="5"/>
     </row>
-    <row r="13" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="5"/>
       <c r="B13" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="5"/>
+      <c r="C13" s="5" t="s">
+        <v>116</v>
+      </c>
       <c r="D13" s="5" t="s">
         <v>58</v>
       </c>
@@ -1914,12 +1934,14 @@
       <c r="AL13" s="5"/>
       <c r="AM13" s="5"/>
     </row>
-    <row r="14" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="5"/>
       <c r="B14" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="5"/>
+      <c r="C14" s="5" t="s">
+        <v>167</v>
+      </c>
       <c r="D14" s="5" t="s">
         <v>58</v>
       </c>
@@ -1981,7 +2003,7 @@
       <c r="AL14" s="5"/>
       <c r="AM14" s="5"/>
     </row>
-    <row r="15" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="5"/>
       <c r="B15" s="5" t="s">
         <v>43</v>
@@ -2050,7 +2072,7 @@
       <c r="AL15" s="5"/>
       <c r="AM15" s="5"/>
     </row>
-    <row r="16" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="5"/>
       <c r="B16" s="5" t="s">
         <v>43</v>
@@ -2119,7 +2141,7 @@
       <c r="AL16" s="5"/>
       <c r="AM16" s="5"/>
     </row>
-    <row r="17" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="5"/>
       <c r="B17" s="5" t="s">
         <v>43</v>
@@ -2188,7 +2210,7 @@
       <c r="AL17" s="5"/>
       <c r="AM17" s="5"/>
     </row>
-    <row r="18" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="5"/>
       <c r="B18" s="5" t="s">
         <v>43</v>
@@ -2257,7 +2279,7 @@
       <c r="AL18" s="5"/>
       <c r="AM18" s="5"/>
     </row>
-    <row r="19" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="5"/>
       <c r="B19" s="5" t="s">
         <v>43</v>
@@ -2326,22 +2348,22 @@
       <c r="AL19" s="5"/>
       <c r="AM19" s="5"/>
     </row>
-    <row r="20" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="5"/>
       <c r="B20" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E20" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F20" s="5" t="s">
         <v>80</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>81</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
@@ -2351,7 +2373,7 @@
       </c>
       <c r="K20" s="5"/>
       <c r="L20" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M20" s="5" t="s">
         <v>49</v>
@@ -2370,7 +2392,7 @@
         <v>51</v>
       </c>
       <c r="S20" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T20" s="5">
         <v>1</v>
@@ -2397,22 +2419,22 @@
       <c r="AL20" s="5"/>
       <c r="AM20" s="5"/>
     </row>
-    <row r="21" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" s="5"/>
       <c r="B21" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E21" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F21" s="5" t="s">
         <v>80</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>81</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
@@ -2422,7 +2444,7 @@
       </c>
       <c r="K21" s="5"/>
       <c r="L21" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M21" s="5" t="s">
         <v>49</v>
@@ -2441,7 +2463,7 @@
         <v>51</v>
       </c>
       <c r="S21" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T21" s="5">
         <v>1</v>
@@ -2468,22 +2490,22 @@
       <c r="AL21" s="5"/>
       <c r="AM21" s="5"/>
     </row>
-    <row r="22" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="5"/>
       <c r="B22" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E22" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F22" s="5" t="s">
         <v>80</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>81</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
@@ -2493,7 +2515,7 @@
       </c>
       <c r="K22" s="5"/>
       <c r="L22" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M22" s="5" t="s">
         <v>49</v>
@@ -2512,7 +2534,7 @@
         <v>51</v>
       </c>
       <c r="S22" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T22" s="5">
         <v>1</v>
@@ -2539,22 +2561,22 @@
       <c r="AL22" s="5"/>
       <c r="AM22" s="5"/>
     </row>
-    <row r="23" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="5"/>
       <c r="B23" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E23" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F23" s="5" t="s">
         <v>80</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>81</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
@@ -2564,7 +2586,7 @@
       </c>
       <c r="K23" s="5"/>
       <c r="L23" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M23" s="5" t="s">
         <v>49</v>
@@ -2583,7 +2605,7 @@
         <v>51</v>
       </c>
       <c r="S23" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T23" s="5">
         <v>1</v>
@@ -2610,22 +2632,22 @@
       <c r="AL23" s="5"/>
       <c r="AM23" s="5"/>
     </row>
-    <row r="24" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="5"/>
       <c r="B24" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E24" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F24" s="5" t="s">
         <v>80</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>81</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
@@ -2635,7 +2657,7 @@
       </c>
       <c r="K24" s="5"/>
       <c r="L24" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M24" s="5" t="s">
         <v>49</v>
@@ -2681,22 +2703,22 @@
       <c r="AL24" s="5"/>
       <c r="AM24" s="5"/>
     </row>
-    <row r="25" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="5"/>
       <c r="B25" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E25" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F25" s="5" t="s">
         <v>80</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>81</v>
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
@@ -2706,7 +2728,7 @@
       </c>
       <c r="K25" s="5"/>
       <c r="L25" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M25" s="5" t="s">
         <v>49</v>
@@ -2752,22 +2774,22 @@
       <c r="AL25" s="5"/>
       <c r="AM25" s="5"/>
     </row>
-    <row r="26" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="5"/>
       <c r="B26" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E26" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>80</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>81</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
@@ -2777,7 +2799,7 @@
       </c>
       <c r="K26" s="5"/>
       <c r="L26" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M26" s="5" t="s">
         <v>49</v>
@@ -2823,22 +2845,22 @@
       <c r="AL26" s="5"/>
       <c r="AM26" s="5"/>
     </row>
-    <row r="27" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="5"/>
       <c r="B27" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E27" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F27" s="5" t="s">
         <v>80</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>81</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
@@ -2848,7 +2870,7 @@
       </c>
       <c r="K27" s="5"/>
       <c r="L27" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M27" s="5" t="s">
         <v>49</v>
@@ -2894,22 +2916,22 @@
       <c r="AL27" s="5"/>
       <c r="AM27" s="5"/>
     </row>
-    <row r="28" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="5"/>
       <c r="B28" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E28" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F28" s="5" t="s">
         <v>80</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>81</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
@@ -2919,7 +2941,7 @@
       </c>
       <c r="K28" s="5"/>
       <c r="L28" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M28" s="5" t="s">
         <v>49</v>
@@ -2938,7 +2960,7 @@
         <v>51</v>
       </c>
       <c r="S28" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T28" s="5">
         <v>1</v>
@@ -2965,22 +2987,22 @@
       <c r="AL28" s="5"/>
       <c r="AM28" s="5"/>
     </row>
-    <row r="29" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="5"/>
       <c r="B29" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E29" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F29" s="5" t="s">
         <v>80</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>81</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
@@ -2990,7 +3012,7 @@
       </c>
       <c r="K29" s="5"/>
       <c r="L29" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M29" s="5" t="s">
         <v>49</v>
@@ -3009,7 +3031,7 @@
         <v>51</v>
       </c>
       <c r="S29" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T29" s="5">
         <v>1</v>
@@ -3036,19 +3058,19 @@
       <c r="AL29" s="5"/>
       <c r="AM29" s="5"/>
     </row>
-    <row r="30" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="5"/>
       <c r="B30" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>88</v>
+        <v>169</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>55</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
@@ -3067,7 +3089,7 @@
         <v>126</v>
       </c>
       <c r="P30" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="Q30" s="5">
         <v>1</v>
@@ -3076,7 +3098,7 @@
         <v>51</v>
       </c>
       <c r="S30" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="T30" s="5">
         <v>1</v>
@@ -3103,19 +3125,19 @@
       <c r="AL30" s="5"/>
       <c r="AM30" s="5"/>
     </row>
-    <row r="31" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="5"/>
       <c r="B31" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>88</v>
+        <v>169</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>55</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
@@ -3134,7 +3156,7 @@
         <v>235</v>
       </c>
       <c r="P31" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="Q31" s="5">
         <v>1</v>
@@ -3170,19 +3192,19 @@
       <c r="AL31" s="5"/>
       <c r="AM31" s="5"/>
     </row>
-    <row r="32" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="5"/>
       <c r="B32" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>88</v>
+        <v>169</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
@@ -3201,7 +3223,7 @@
         <v>1152</v>
       </c>
       <c r="P32" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="Q32" s="5">
         <v>1</v>
@@ -3237,13 +3259,13 @@
       <c r="AL32" s="5"/>
       <c r="AM32" s="5"/>
     </row>
-    <row r="33" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="5"/>
       <c r="B33" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>45</v>
@@ -3265,7 +3287,7 @@
         <v>48</v>
       </c>
       <c r="M33" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N33" s="5"/>
       <c r="O33" s="5"/>
@@ -3297,13 +3319,13 @@
       <c r="AC33" s="5"/>
       <c r="AD33" s="5"/>
       <c r="AE33" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AF33" s="5" t="s">
         <v>44</v>
       </c>
       <c r="AG33" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="AH33" s="5"/>
       <c r="AI33" s="5"/>
@@ -3324,16 +3346,16 @@
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="34" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="5"/>
       <c r="B34" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>59</v>
@@ -3352,7 +3374,7 @@
         <v>54</v>
       </c>
       <c r="M34" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N34" s="5"/>
       <c r="O34" s="5"/>
@@ -3384,13 +3406,13 @@
       <c r="AC34" s="5"/>
       <c r="AD34" s="5"/>
       <c r="AE34" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AF34" s="5" t="s">
         <v>44</v>
       </c>
       <c r="AG34" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="AH34" s="5"/>
       <c r="AI34" s="5"/>
@@ -3411,13 +3433,13 @@
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="35" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="5"/>
       <c r="B35" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>45</v>
@@ -3439,7 +3461,7 @@
         <v>48</v>
       </c>
       <c r="M35" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N35" s="5"/>
       <c r="O35" s="5"/>
@@ -3471,13 +3493,13 @@
       <c r="AC35" s="5"/>
       <c r="AD35" s="5"/>
       <c r="AE35" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="AF35" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="AG35" s="5" t="s">
         <v>97</v>
-      </c>
-      <c r="AF35" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="AG35" s="5" t="s">
-        <v>99</v>
       </c>
       <c r="AH35" s="5"/>
       <c r="AI35" s="5"/>
@@ -3486,16 +3508,16 @@
       <c r="AL35" s="5"/>
       <c r="AM35" s="5"/>
     </row>
-    <row r="36" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="5"/>
       <c r="B36" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E36" s="5" t="s">
         <v>59</v>
@@ -3514,7 +3536,7 @@
         <v>54</v>
       </c>
       <c r="M36" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N36" s="5"/>
       <c r="O36" s="5"/>
@@ -3546,13 +3568,13 @@
       <c r="AC36" s="5"/>
       <c r="AD36" s="5"/>
       <c r="AE36" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="AF36" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="AG36" s="5" t="s">
         <v>97</v>
-      </c>
-      <c r="AF36" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="AG36" s="5" t="s">
-        <v>99</v>
       </c>
       <c r="AH36" s="5"/>
       <c r="AI36" s="5"/>
@@ -3561,13 +3583,13 @@
       <c r="AL36" s="5"/>
       <c r="AM36" s="5"/>
     </row>
-    <row r="37" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="5"/>
       <c r="B37" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>45</v>
@@ -3586,10 +3608,10 @@
       </c>
       <c r="K37" s="5"/>
       <c r="L37" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M37" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N37" s="5"/>
       <c r="O37" s="5"/>
@@ -3621,13 +3643,13 @@
       <c r="AC37" s="5"/>
       <c r="AD37" s="5"/>
       <c r="AE37" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AF37" s="5" t="s">
         <v>44</v>
       </c>
       <c r="AG37" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AH37" s="5"/>
       <c r="AI37" s="5"/>
@@ -3648,16 +3670,16 @@
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="5"/>
       <c r="B38" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E38" s="5" t="s">
         <v>59</v>
@@ -3673,10 +3695,10 @@
       </c>
       <c r="K38" s="5"/>
       <c r="L38" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="M38" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N38" s="5"/>
       <c r="O38" s="5"/>
@@ -3708,13 +3730,13 @@
       <c r="AC38" s="5"/>
       <c r="AD38" s="5"/>
       <c r="AE38" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AF38" s="5" t="s">
         <v>44</v>
       </c>
       <c r="AG38" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AH38" s="5"/>
       <c r="AI38" s="5"/>
@@ -3735,13 +3757,13 @@
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="5"/>
       <c r="B39" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>45</v>
@@ -3760,10 +3782,10 @@
       </c>
       <c r="K39" s="5"/>
       <c r="L39" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="M39" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N39" s="5"/>
       <c r="O39" s="5"/>
@@ -3795,13 +3817,13 @@
       <c r="AC39" s="5"/>
       <c r="AD39" s="5"/>
       <c r="AE39" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="AF39" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="AG39" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="AH39" s="5"/>
       <c r="AI39" s="5"/>
@@ -3810,16 +3832,16 @@
       <c r="AL39" s="5"/>
       <c r="AM39" s="5"/>
     </row>
-    <row r="40" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A40" s="5"/>
       <c r="B40" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E40" s="5" t="s">
         <v>59</v>
@@ -3835,10 +3857,10 @@
       </c>
       <c r="K40" s="5"/>
       <c r="L40" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M40" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N40" s="5"/>
       <c r="O40" s="5"/>
@@ -3870,13 +3892,13 @@
       <c r="AC40" s="5"/>
       <c r="AD40" s="5"/>
       <c r="AE40" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="AF40" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="AG40" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="AH40" s="5"/>
       <c r="AI40" s="5"/>
@@ -3885,13 +3907,13 @@
       <c r="AL40" s="5"/>
       <c r="AM40" s="5"/>
     </row>
-    <row r="41" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="5"/>
       <c r="B41" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>74</v>
@@ -3954,13 +3976,13 @@
       <c r="AL41" s="5"/>
       <c r="AM41" s="5"/>
     </row>
-    <row r="42" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" s="5"/>
       <c r="B42" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>45</v>
@@ -4027,13 +4049,13 @@
       <c r="AL42" s="5"/>
       <c r="AM42" s="5"/>
     </row>
-    <row r="43" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="5"/>
       <c r="B43" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>45</v>
@@ -4100,13 +4122,13 @@
       <c r="AL43" s="5"/>
       <c r="AM43" s="5"/>
     </row>
-    <row r="44" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="5"/>
       <c r="B44" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>45</v>
@@ -4173,13 +4195,13 @@
       <c r="AL44" s="5"/>
       <c r="AM44" s="5"/>
     </row>
-    <row r="45" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="5"/>
       <c r="B45" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>45</v>
@@ -4246,13 +4268,13 @@
       <c r="AL45" s="5"/>
       <c r="AM45" s="5"/>
     </row>
-    <row r="46" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" s="5"/>
       <c r="B46" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>74</v>
@@ -4317,13 +4339,13 @@
       <c r="AL46" s="5"/>
       <c r="AM46" s="5"/>
     </row>
-    <row r="47" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="5"/>
       <c r="B47" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>45</v>
@@ -4345,7 +4367,7 @@
         <v>48</v>
       </c>
       <c r="M47" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N47" s="5"/>
       <c r="O47" s="5"/>
@@ -4377,13 +4399,13 @@
       <c r="AC47" s="5"/>
       <c r="AD47" s="5"/>
       <c r="AE47" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF47" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG47" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH47" s="5"/>
       <c r="AI47" s="5"/>
@@ -4392,16 +4414,16 @@
       <c r="AL47" s="5"/>
       <c r="AM47" s="5"/>
     </row>
-    <row r="48" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" s="5"/>
       <c r="B48" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E48" s="5" t="s">
         <v>68</v>
@@ -4420,7 +4442,7 @@
         <v>54</v>
       </c>
       <c r="M48" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N48" s="5"/>
       <c r="O48" s="5"/>
@@ -4452,13 +4474,13 @@
       <c r="AC48" s="5"/>
       <c r="AD48" s="5"/>
       <c r="AE48" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AF48" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG48" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AH48" s="5"/>
       <c r="AI48" s="5"/>
@@ -4467,13 +4489,13 @@
       <c r="AL48" s="5"/>
       <c r="AM48" s="5"/>
     </row>
-    <row r="49" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="5"/>
       <c r="B49" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>45</v>
@@ -4495,7 +4517,7 @@
         <v>48</v>
       </c>
       <c r="M49" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N49" s="5"/>
       <c r="O49" s="5"/>
@@ -4527,13 +4549,13 @@
       <c r="AC49" s="5"/>
       <c r="AD49" s="5"/>
       <c r="AE49" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AF49" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="AG49" s="5" t="s">
         <v>111</v>
-      </c>
-      <c r="AG49" s="5" t="s">
-        <v>113</v>
       </c>
       <c r="AH49" s="5"/>
       <c r="AI49" s="5"/>
@@ -4542,16 +4564,16 @@
       <c r="AL49" s="5"/>
       <c r="AM49" s="5"/>
     </row>
-    <row r="50" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" s="5"/>
       <c r="B50" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>68</v>
@@ -4570,7 +4592,7 @@
         <v>54</v>
       </c>
       <c r="M50" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N50" s="5"/>
       <c r="O50" s="5"/>
@@ -4602,13 +4624,13 @@
       <c r="AC50" s="5"/>
       <c r="AD50" s="5"/>
       <c r="AE50" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="AF50" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG50" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="AH50" s="5"/>
       <c r="AI50" s="5"/>
@@ -4617,13 +4639,13 @@
       <c r="AL50" s="5"/>
       <c r="AM50" s="5"/>
     </row>
-    <row r="51" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51" s="5"/>
       <c r="B51" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>57</v>
@@ -4686,13 +4708,13 @@
       <c r="AL51" s="5"/>
       <c r="AM51" s="5"/>
     </row>
-    <row r="52" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" s="5"/>
       <c r="B52" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>115</v>
+        <v>170</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>57</v>
@@ -4755,13 +4777,13 @@
       <c r="AL52" s="5"/>
       <c r="AM52" s="5"/>
     </row>
-    <row r="53" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" s="5"/>
       <c r="B53" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>74</v>
@@ -4824,13 +4846,13 @@
       <c r="AL53" s="5"/>
       <c r="AM53" s="5"/>
     </row>
-    <row r="54" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A54" s="5"/>
       <c r="B54" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>115</v>
+        <v>170</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>74</v>
@@ -4893,13 +4915,13 @@
       <c r="AL54" s="5"/>
       <c r="AM54" s="5"/>
     </row>
-    <row r="55" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A55" s="5"/>
       <c r="B55" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>45</v>
@@ -4964,13 +4986,13 @@
       <c r="AL55" s="5"/>
       <c r="AM55" s="5"/>
     </row>
-    <row r="56" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A56" s="5"/>
       <c r="B56" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D56" s="5" t="s">
         <v>45</v>
@@ -5035,13 +5057,13 @@
       <c r="AL56" s="5"/>
       <c r="AM56" s="5"/>
     </row>
-    <row r="57" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A57" s="5"/>
       <c r="B57" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>45</v>
@@ -5106,13 +5128,13 @@
       <c r="AL57" s="5"/>
       <c r="AM57" s="5"/>
     </row>
-    <row r="58" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A58" s="5"/>
       <c r="B58" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D58" s="5" t="s">
         <v>45</v>
@@ -5177,13 +5199,13 @@
       <c r="AL58" s="5"/>
       <c r="AM58" s="5"/>
     </row>
-    <row r="59" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A59" s="5"/>
       <c r="B59" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>57</v>
@@ -5246,13 +5268,13 @@
       <c r="AL59" s="5"/>
       <c r="AM59" s="5"/>
     </row>
-    <row r="60" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A60" s="5"/>
       <c r="B60" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>74</v>
@@ -5315,19 +5337,19 @@
       <c r="AL60" s="5"/>
       <c r="AM60" s="5"/>
     </row>
-    <row r="61" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A61" s="5"/>
       <c r="B61" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="5"/>
@@ -5384,13 +5406,13 @@
       <c r="AL61" s="5"/>
       <c r="AM61" s="5"/>
     </row>
-    <row r="62" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A62" s="5"/>
       <c r="B62" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>45</v>
@@ -5455,13 +5477,13 @@
       <c r="AL62" s="5"/>
       <c r="AM62" s="5"/>
     </row>
-    <row r="63" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A63" s="5"/>
       <c r="B63" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>45</v>
@@ -5526,13 +5548,13 @@
       <c r="AL63" s="5"/>
       <c r="AM63" s="5"/>
     </row>
-    <row r="64" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A64" s="5"/>
       <c r="B64" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>74</v>
@@ -5595,13 +5617,13 @@
       <c r="AL64" s="5"/>
       <c r="AM64" s="5"/>
     </row>
-    <row r="65" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A65" s="5"/>
       <c r="B65" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>74</v>
@@ -5664,22 +5686,22 @@
       <c r="AL65" s="5"/>
       <c r="AM65" s="5"/>
     </row>
-    <row r="66" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A66" s="5"/>
       <c r="B66" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="5" t="s">
@@ -5694,7 +5716,7 @@
         <v>48</v>
       </c>
       <c r="M66" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N66" s="5"/>
       <c r="O66" s="5"/>
@@ -5726,13 +5748,13 @@
       <c r="AC66" s="5"/>
       <c r="AD66" s="5"/>
       <c r="AE66" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="AF66" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG66" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="AH66" s="5"/>
       <c r="AI66" s="5"/>
@@ -5747,22 +5769,22 @@
       </c>
       <c r="AM66" s="5"/>
     </row>
-    <row r="67" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A67" s="5"/>
       <c r="B67" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="5" t="s">
@@ -5777,7 +5799,7 @@
         <v>54</v>
       </c>
       <c r="M67" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N67" s="5"/>
       <c r="O67" s="5"/>
@@ -5809,13 +5831,13 @@
       <c r="AC67" s="5"/>
       <c r="AD67" s="5"/>
       <c r="AE67" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="AF67" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG67" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="AH67" s="5"/>
       <c r="AI67" s="5"/>
@@ -5830,22 +5852,22 @@
       </c>
       <c r="AM67" s="5"/>
     </row>
-    <row r="68" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A68" s="5"/>
       <c r="B68" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="5" t="s">
@@ -5860,7 +5882,7 @@
         <v>48</v>
       </c>
       <c r="M68" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N68" s="5"/>
       <c r="O68" s="5"/>
@@ -5892,13 +5914,13 @@
       <c r="AC68" s="5"/>
       <c r="AD68" s="5"/>
       <c r="AE68" s="5" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="AF68" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG68" s="5" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="AH68" s="5"/>
       <c r="AI68" s="5"/>
@@ -5913,22 +5935,22 @@
       </c>
       <c r="AM68" s="5"/>
     </row>
-    <row r="69" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A69" s="5"/>
       <c r="B69" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G69" s="5"/>
       <c r="H69" s="5" t="s">
@@ -5943,7 +5965,7 @@
         <v>54</v>
       </c>
       <c r="M69" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N69" s="5"/>
       <c r="O69" s="5"/>
@@ -5975,13 +5997,13 @@
       <c r="AC69" s="5"/>
       <c r="AD69" s="5"/>
       <c r="AE69" s="5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AF69" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG69" s="5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AH69" s="5"/>
       <c r="AI69" s="5"/>
@@ -5996,22 +6018,22 @@
       </c>
       <c r="AM69" s="5"/>
     </row>
-    <row r="70" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A70" s="5"/>
       <c r="B70" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D70" s="5" t="s">
         <v>74</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="5"/>
@@ -6065,22 +6087,22 @@
       <c r="AL70" s="5"/>
       <c r="AM70" s="5"/>
     </row>
-    <row r="71" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A71" s="5"/>
       <c r="B71" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="5"/>
@@ -6134,22 +6156,22 @@
       <c r="AL71" s="5"/>
       <c r="AM71" s="5"/>
     </row>
-    <row r="72" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A72" s="5"/>
       <c r="B72" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D72" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="5" t="s">
@@ -6207,22 +6229,22 @@
       <c r="AL72" s="5"/>
       <c r="AM72" s="5"/>
     </row>
-    <row r="73" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A73" s="5"/>
       <c r="B73" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D73" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G73" s="5"/>
       <c r="H73" s="5" t="s">
@@ -6280,22 +6302,22 @@
       <c r="AL73" s="5"/>
       <c r="AM73" s="5"/>
     </row>
-    <row r="74" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A74" s="5"/>
       <c r="B74" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D74" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="5" t="s">
@@ -6353,22 +6375,22 @@
       <c r="AL74" s="5"/>
       <c r="AM74" s="5"/>
     </row>
-    <row r="75" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A75" s="5"/>
       <c r="B75" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D75" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G75" s="5"/>
       <c r="H75" s="5" t="s">
@@ -6426,22 +6448,22 @@
       <c r="AL75" s="5"/>
       <c r="AM75" s="5"/>
     </row>
-    <row r="76" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A76" s="5"/>
       <c r="B76" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D76" s="5" t="s">
         <v>74</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G76" s="5"/>
       <c r="H76" s="5"/>
@@ -6495,22 +6517,22 @@
       <c r="AL76" s="5"/>
       <c r="AM76" s="5"/>
     </row>
-    <row r="77" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A77" s="5"/>
       <c r="B77" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D77" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G77" s="5"/>
       <c r="H77" s="5" t="s">
@@ -6566,22 +6588,22 @@
       <c r="AL77" s="5"/>
       <c r="AM77" s="5"/>
     </row>
-    <row r="78" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A78" s="5"/>
       <c r="B78" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D78" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G78" s="5"/>
       <c r="H78" s="5" t="s">
@@ -6639,22 +6661,22 @@
       <c r="AL78" s="5"/>
       <c r="AM78" s="5"/>
     </row>
-    <row r="79" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A79" s="5"/>
       <c r="B79" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D79" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G79" s="5"/>
       <c r="H79" s="5" t="s">
@@ -6712,22 +6734,22 @@
       <c r="AL79" s="5"/>
       <c r="AM79" s="5"/>
     </row>
-    <row r="80" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A80" s="5"/>
       <c r="B80" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D80" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G80" s="5"/>
       <c r="H80" s="5" t="s">
@@ -6785,22 +6807,22 @@
       <c r="AL80" s="5"/>
       <c r="AM80" s="5"/>
     </row>
-    <row r="81" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A81" s="5"/>
       <c r="B81" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D81" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G81" s="5"/>
       <c r="H81" s="5"/>
@@ -6854,22 +6876,22 @@
       <c r="AL81" s="5"/>
       <c r="AM81" s="5"/>
     </row>
-    <row r="82" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A82" s="5"/>
       <c r="B82" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D82" s="5" t="s">
         <v>74</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G82" s="5"/>
       <c r="H82" s="5"/>
@@ -6923,22 +6945,22 @@
       <c r="AL82" s="5"/>
       <c r="AM82" s="5"/>
     </row>
-    <row r="83" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A83" s="5"/>
       <c r="B83" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G83" s="5"/>
       <c r="H83" s="5"/>
@@ -6992,22 +7014,22 @@
       <c r="AL83" s="5"/>
       <c r="AM83" s="5"/>
     </row>
-    <row r="84" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A84" s="5"/>
       <c r="B84" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D84" s="5" t="s">
         <v>74</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G84" s="5"/>
       <c r="H84" s="5"/>
@@ -7017,7 +7039,7 @@
       </c>
       <c r="K84" s="5"/>
       <c r="L84" s="5" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="M84" s="5" t="s">
         <v>49</v>
@@ -7063,22 +7085,22 @@
       <c r="AL84" s="5"/>
       <c r="AM84" s="5"/>
     </row>
-    <row r="85" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A85" s="5"/>
       <c r="B85" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D85" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G85" s="5"/>
       <c r="H85" s="5" t="s">
@@ -7093,7 +7115,7 @@
         <v>48</v>
       </c>
       <c r="M85" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N85" s="5"/>
       <c r="O85" s="5"/>
@@ -7125,13 +7147,13 @@
       <c r="AC85" s="5"/>
       <c r="AD85" s="5"/>
       <c r="AE85" s="5" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="AF85" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG85" s="5" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="AH85" s="5">
         <v>1.1366719999999999</v>
@@ -7150,22 +7172,22 @@
       </c>
       <c r="AM85" s="5"/>
     </row>
-    <row r="86" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A86" s="5"/>
       <c r="B86" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G86" s="5"/>
       <c r="H86" s="5" t="s">
@@ -7180,7 +7202,7 @@
         <v>54</v>
       </c>
       <c r="M86" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N86" s="5"/>
       <c r="O86" s="5"/>
@@ -7212,13 +7234,13 @@
       <c r="AC86" s="5"/>
       <c r="AD86" s="5"/>
       <c r="AE86" s="5" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="AF86" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG86" s="5" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="AH86" s="5">
         <v>1.1366719999999999</v>
@@ -7237,22 +7259,22 @@
       </c>
       <c r="AM86" s="5"/>
     </row>
-    <row r="87" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A87" s="5"/>
       <c r="B87" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D87" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G87" s="5"/>
       <c r="H87" s="5" t="s">
@@ -7267,7 +7289,7 @@
         <v>48</v>
       </c>
       <c r="M87" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N87" s="5"/>
       <c r="O87" s="5"/>
@@ -7299,13 +7321,13 @@
       <c r="AC87" s="5"/>
       <c r="AD87" s="5"/>
       <c r="AE87" s="5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="AF87" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG87" s="5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="AH87" s="5">
         <v>1.101672</v>
@@ -7324,22 +7346,22 @@
       </c>
       <c r="AM87" s="5"/>
     </row>
-    <row r="88" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A88" s="5"/>
       <c r="B88" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G88" s="5"/>
       <c r="H88" s="5" t="s">
@@ -7354,7 +7376,7 @@
         <v>54</v>
       </c>
       <c r="M88" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N88" s="5"/>
       <c r="O88" s="5"/>
@@ -7386,13 +7408,13 @@
       <c r="AC88" s="5"/>
       <c r="AD88" s="5"/>
       <c r="AE88" s="5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="AF88" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG88" s="5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="AH88" s="5">
         <v>1.101672</v>
@@ -7411,22 +7433,22 @@
       </c>
       <c r="AM88" s="5"/>
     </row>
-    <row r="89" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A89" s="5"/>
       <c r="B89" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D89" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G89" s="5"/>
       <c r="H89" s="5"/>
@@ -7480,22 +7502,22 @@
       <c r="AL89" s="5"/>
       <c r="AM89" s="5"/>
     </row>
-    <row r="90" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A90" s="5"/>
       <c r="B90" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D90" s="5" t="s">
         <v>74</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G90" s="5"/>
       <c r="H90" s="5"/>
@@ -7549,22 +7571,22 @@
       <c r="AL90" s="5"/>
       <c r="AM90" s="5"/>
     </row>
-    <row r="91" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A91" s="5"/>
       <c r="B91" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G91" s="5"/>
       <c r="H91" s="5"/>
@@ -7618,22 +7640,22 @@
       <c r="AL91" s="5"/>
       <c r="AM91" s="5"/>
     </row>
-    <row r="92" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A92" s="5"/>
       <c r="B92" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="D92" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G92" s="5"/>
       <c r="H92" s="5" t="s">
@@ -7648,7 +7670,7 @@
         <v>48</v>
       </c>
       <c r="M92" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N92" s="5"/>
       <c r="O92" s="5"/>
@@ -7680,13 +7702,13 @@
       <c r="AC92" s="5"/>
       <c r="AD92" s="5"/>
       <c r="AE92" s="5" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AF92" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG92" s="5" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AH92" s="5"/>
       <c r="AI92" s="5"/>
@@ -7701,22 +7723,22 @@
       </c>
       <c r="AM92" s="5"/>
     </row>
-    <row r="93" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A93" s="5"/>
       <c r="B93" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G93" s="5"/>
       <c r="H93" s="5" t="s">
@@ -7731,7 +7753,7 @@
         <v>54</v>
       </c>
       <c r="M93" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N93" s="5"/>
       <c r="O93" s="5"/>
@@ -7763,13 +7785,13 @@
       <c r="AC93" s="5"/>
       <c r="AD93" s="5"/>
       <c r="AE93" s="5" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AF93" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG93" s="5" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AH93" s="5"/>
       <c r="AI93" s="5"/>
@@ -7784,22 +7806,22 @@
       </c>
       <c r="AM93" s="5"/>
     </row>
-    <row r="94" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A94" s="5"/>
       <c r="B94" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="D94" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G94" s="5"/>
       <c r="H94" s="5" t="s">
@@ -7814,7 +7836,7 @@
         <v>48</v>
       </c>
       <c r="M94" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N94" s="5"/>
       <c r="O94" s="5"/>
@@ -7846,13 +7868,13 @@
       <c r="AC94" s="5"/>
       <c r="AD94" s="5"/>
       <c r="AE94" s="5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="AF94" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG94" s="5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="AH94" s="5"/>
       <c r="AI94" s="5"/>
@@ -7867,22 +7889,22 @@
       </c>
       <c r="AM94" s="5"/>
     </row>
-    <row r="95" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A95" s="5"/>
       <c r="B95" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G95" s="5"/>
       <c r="H95" s="5" t="s">
@@ -7897,7 +7919,7 @@
         <v>54</v>
       </c>
       <c r="M95" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N95" s="5"/>
       <c r="O95" s="5"/>
@@ -7929,13 +7951,13 @@
       <c r="AC95" s="5"/>
       <c r="AD95" s="5"/>
       <c r="AE95" s="5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="AF95" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG95" s="5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="AH95" s="5"/>
       <c r="AI95" s="5"/>
@@ -7950,22 +7972,22 @@
       </c>
       <c r="AM95" s="5"/>
     </row>
-    <row r="96" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A96" s="5"/>
       <c r="B96" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="D96" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G96" s="5"/>
       <c r="H96" s="5"/>
@@ -8019,22 +8041,22 @@
       <c r="AL96" s="5"/>
       <c r="AM96" s="5"/>
     </row>
-    <row r="97" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A97" s="5"/>
       <c r="B97" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="D97" s="5" t="s">
         <v>74</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G97" s="5"/>
       <c r="H97" s="5"/>
@@ -8088,22 +8110,22 @@
       <c r="AL97" s="5"/>
       <c r="AM97" s="5"/>
     </row>
-    <row r="98" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A98" s="5"/>
       <c r="B98" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G98" s="5"/>
       <c r="H98" s="5"/>
@@ -8157,22 +8179,22 @@
       <c r="AL98" s="5"/>
       <c r="AM98" s="5"/>
     </row>
-    <row r="99" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A99" s="5"/>
       <c r="B99" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="D99" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G99" s="5"/>
       <c r="H99" s="5" t="s">
@@ -8230,22 +8252,22 @@
       <c r="AL99" s="5"/>
       <c r="AM99" s="5"/>
     </row>
-    <row r="100" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A100" s="5"/>
       <c r="B100" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="D100" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G100" s="5"/>
       <c r="H100" s="5" t="s">
@@ -8303,22 +8325,22 @@
       <c r="AL100" s="5"/>
       <c r="AM100" s="5"/>
     </row>
-    <row r="101" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A101" s="5"/>
       <c r="B101" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="D101" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G101" s="5"/>
       <c r="H101" s="5" t="s">
@@ -8376,22 +8398,22 @@
       <c r="AL101" s="5"/>
       <c r="AM101" s="5"/>
     </row>
-    <row r="102" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A102" s="5"/>
       <c r="B102" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="D102" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G102" s="5"/>
       <c r="H102" s="5" t="s">
@@ -8449,22 +8471,22 @@
       <c r="AL102" s="5"/>
       <c r="AM102" s="5"/>
     </row>
-    <row r="103" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A103" s="5"/>
       <c r="B103" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="D103" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G103" s="5"/>
       <c r="H103" s="5"/>
@@ -8518,22 +8540,22 @@
       <c r="AL103" s="5"/>
       <c r="AM103" s="5"/>
     </row>
-    <row r="104" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A104" s="5"/>
       <c r="B104" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="D104" s="5" t="s">
         <v>74</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G104" s="5"/>
       <c r="H104" s="5"/>
@@ -8587,22 +8609,22 @@
       <c r="AL104" s="5"/>
       <c r="AM104" s="5"/>
     </row>
-    <row r="105" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A105" s="5"/>
       <c r="B105" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G105" s="5"/>
       <c r="H105" s="5"/>
@@ -8656,22 +8678,22 @@
       <c r="AL105" s="5"/>
       <c r="AM105" s="5"/>
     </row>
-    <row r="106" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A106" s="5"/>
       <c r="B106" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D106" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G106" s="5"/>
       <c r="H106" s="5" t="s">
@@ -8686,7 +8708,7 @@
         <v>48</v>
       </c>
       <c r="M106" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N106" s="5"/>
       <c r="O106" s="5"/>
@@ -8718,13 +8740,13 @@
       <c r="AC106" s="5"/>
       <c r="AD106" s="5"/>
       <c r="AE106" s="5" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AF106" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG106" s="5" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AH106" s="5"/>
       <c r="AI106" s="5"/>
@@ -8739,22 +8761,22 @@
       </c>
       <c r="AM106" s="5"/>
     </row>
-    <row r="107" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A107" s="5"/>
       <c r="B107" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G107" s="5"/>
       <c r="H107" s="5" t="s">
@@ -8769,7 +8791,7 @@
         <v>54</v>
       </c>
       <c r="M107" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N107" s="5"/>
       <c r="O107" s="5"/>
@@ -8801,13 +8823,13 @@
       <c r="AC107" s="5"/>
       <c r="AD107" s="5"/>
       <c r="AE107" s="5" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AF107" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG107" s="5" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AH107" s="5"/>
       <c r="AI107" s="5"/>
@@ -8822,22 +8844,22 @@
       </c>
       <c r="AM107" s="5"/>
     </row>
-    <row r="108" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A108" s="5"/>
       <c r="B108" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D108" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G108" s="5"/>
       <c r="H108" s="5" t="s">
@@ -8852,7 +8874,7 @@
         <v>48</v>
       </c>
       <c r="M108" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N108" s="5"/>
       <c r="O108" s="5"/>
@@ -8884,13 +8906,13 @@
       <c r="AC108" s="5"/>
       <c r="AD108" s="5"/>
       <c r="AE108" s="5" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="AF108" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG108" s="5" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="AH108" s="5"/>
       <c r="AI108" s="5"/>
@@ -8905,22 +8927,22 @@
       </c>
       <c r="AM108" s="5"/>
     </row>
-    <row r="109" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A109" s="5"/>
       <c r="B109" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G109" s="5"/>
       <c r="H109" s="5" t="s">
@@ -8935,7 +8957,7 @@
         <v>54</v>
       </c>
       <c r="M109" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N109" s="5"/>
       <c r="O109" s="5"/>
@@ -8967,13 +8989,13 @@
       <c r="AC109" s="5"/>
       <c r="AD109" s="5"/>
       <c r="AE109" s="5" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="AF109" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG109" s="5" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="AH109" s="5"/>
       <c r="AI109" s="5"/>
@@ -8988,22 +9010,22 @@
       </c>
       <c r="AM109" s="5"/>
     </row>
-    <row r="110" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A110" s="5"/>
       <c r="B110" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D110" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G110" s="5"/>
       <c r="H110" s="5"/>
@@ -9057,22 +9079,22 @@
       <c r="AL110" s="5"/>
       <c r="AM110" s="5"/>
     </row>
-    <row r="111" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A111" s="5"/>
       <c r="B111" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D111" s="5" t="s">
         <v>74</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G111" s="5"/>
       <c r="H111" s="5"/>
@@ -9126,22 +9148,22 @@
       <c r="AL111" s="5"/>
       <c r="AM111" s="5"/>
     </row>
-    <row r="112" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A112" s="5"/>
       <c r="B112" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D112" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G112" s="5"/>
       <c r="H112" s="5" t="s">
@@ -9199,22 +9221,22 @@
       <c r="AL112" s="5"/>
       <c r="AM112" s="5"/>
     </row>
-    <row r="113" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A113" s="5"/>
       <c r="B113" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D113" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G113" s="5"/>
       <c r="H113" s="5" t="s">
@@ -9272,22 +9294,22 @@
       <c r="AL113" s="5"/>
       <c r="AM113" s="5"/>
     </row>
-    <row r="114" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A114" s="5"/>
       <c r="B114" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D114" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G114" s="5"/>
       <c r="H114" s="5" t="s">
@@ -9345,22 +9367,22 @@
       <c r="AL114" s="5"/>
       <c r="AM114" s="5"/>
     </row>
-    <row r="115" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A115" s="5"/>
       <c r="B115" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D115" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G115" s="5"/>
       <c r="H115" s="5" t="s">
@@ -9418,22 +9440,22 @@
       <c r="AL115" s="5"/>
       <c r="AM115" s="5"/>
     </row>
-    <row r="116" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A116" s="5"/>
       <c r="B116" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D116" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G116" s="5"/>
       <c r="H116" s="5"/>
@@ -9487,22 +9509,22 @@
       <c r="AL116" s="5"/>
       <c r="AM116" s="5"/>
     </row>
-    <row r="117" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A117" s="5"/>
       <c r="B117" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D117" s="5" t="s">
         <v>74</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G117" s="5"/>
       <c r="H117" s="5"/>
@@ -9556,22 +9578,22 @@
       <c r="AL117" s="5"/>
       <c r="AM117" s="5"/>
     </row>
-    <row r="118" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A118" s="5"/>
       <c r="B118" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G118" s="5"/>
       <c r="H118" s="5"/>
@@ -9625,22 +9647,22 @@
       <c r="AL118" s="5"/>
       <c r="AM118" s="5"/>
     </row>
-    <row r="119" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A119" s="5"/>
       <c r="B119" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G119" s="5"/>
       <c r="H119" s="5"/>
@@ -9658,7 +9680,7 @@
         <v>0.3</v>
       </c>
       <c r="P119" s="5" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="Q119" s="5">
         <v>30</v>
@@ -9694,22 +9716,22 @@
       <c r="AL119" s="5"/>
       <c r="AM119" s="5"/>
     </row>
-    <row r="120" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A120" s="5"/>
       <c r="B120" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D120" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G120" s="5"/>
       <c r="H120" s="5" t="s">
@@ -9724,7 +9746,7 @@
         <v>48</v>
       </c>
       <c r="M120" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N120" s="5"/>
       <c r="O120" s="5"/>
@@ -9756,13 +9778,13 @@
       <c r="AC120" s="5"/>
       <c r="AD120" s="5"/>
       <c r="AE120" s="5" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="AF120" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG120" s="5" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="AH120" s="5"/>
       <c r="AI120" s="5"/>
@@ -9777,22 +9799,22 @@
       </c>
       <c r="AM120" s="5"/>
     </row>
-    <row r="121" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A121" s="5"/>
       <c r="B121" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G121" s="5"/>
       <c r="H121" s="5" t="s">
@@ -9807,7 +9829,7 @@
         <v>54</v>
       </c>
       <c r="M121" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N121" s="5"/>
       <c r="O121" s="5"/>
@@ -9839,13 +9861,13 @@
       <c r="AC121" s="5"/>
       <c r="AD121" s="5"/>
       <c r="AE121" s="5" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="AF121" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG121" s="5" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="AH121" s="5"/>
       <c r="AI121" s="5"/>
@@ -9860,22 +9882,22 @@
       </c>
       <c r="AM121" s="5"/>
     </row>
-    <row r="122" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A122" s="5"/>
       <c r="B122" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D122" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G122" s="5"/>
       <c r="H122" s="5" t="s">
@@ -9890,7 +9912,7 @@
         <v>48</v>
       </c>
       <c r="M122" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N122" s="5"/>
       <c r="O122" s="5"/>
@@ -9922,13 +9944,13 @@
       <c r="AC122" s="5"/>
       <c r="AD122" s="5"/>
       <c r="AE122" s="5" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="AF122" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG122" s="5" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="AH122" s="5"/>
       <c r="AI122" s="5"/>
@@ -9943,22 +9965,22 @@
       </c>
       <c r="AM122" s="5"/>
     </row>
-    <row r="123" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A123" s="5"/>
       <c r="B123" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G123" s="5"/>
       <c r="H123" s="5" t="s">
@@ -9973,7 +9995,7 @@
         <v>54</v>
       </c>
       <c r="M123" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N123" s="5"/>
       <c r="O123" s="5"/>
@@ -10005,13 +10027,13 @@
       <c r="AC123" s="5"/>
       <c r="AD123" s="5"/>
       <c r="AE123" s="5" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="AF123" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG123" s="5" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="AH123" s="5"/>
       <c r="AI123" s="5"/>
@@ -10026,22 +10048,22 @@
       </c>
       <c r="AM123" s="5"/>
     </row>
-    <row r="124" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A124" s="5"/>
       <c r="B124" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D124" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G124" s="5"/>
       <c r="H124" s="5"/>
@@ -10095,22 +10117,22 @@
       <c r="AL124" s="5"/>
       <c r="AM124" s="5"/>
     </row>
-    <row r="125" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A125" s="5"/>
       <c r="B125" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D125" s="5" t="s">
         <v>74</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G125" s="5"/>
       <c r="H125" s="5"/>
@@ -10164,22 +10186,22 @@
       <c r="AL125" s="5"/>
       <c r="AM125" s="5"/>
     </row>
-    <row r="126" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A126" s="5"/>
       <c r="B126" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G126" s="5"/>
       <c r="H126" s="5"/>
@@ -10233,22 +10255,22 @@
       <c r="AL126" s="5"/>
       <c r="AM126" s="5"/>
     </row>
-    <row r="127" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A127" s="5"/>
       <c r="B127" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D127" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G127" s="5"/>
       <c r="H127" s="5" t="s">
@@ -10263,7 +10285,7 @@
         <v>48</v>
       </c>
       <c r="M127" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N127" s="5"/>
       <c r="O127" s="5"/>
@@ -10295,13 +10317,13 @@
       <c r="AC127" s="5"/>
       <c r="AD127" s="5"/>
       <c r="AE127" s="5" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="AF127" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG127" s="5" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="AH127" s="5">
         <v>1.4620299999999999</v>
@@ -10320,22 +10342,22 @@
       </c>
       <c r="AM127" s="5"/>
     </row>
-    <row r="128" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A128" s="5"/>
       <c r="B128" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G128" s="5"/>
       <c r="H128" s="5" t="s">
@@ -10350,7 +10372,7 @@
         <v>54</v>
       </c>
       <c r="M128" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N128" s="5"/>
       <c r="O128" s="5"/>
@@ -10382,13 +10404,13 @@
       <c r="AC128" s="5"/>
       <c r="AD128" s="5"/>
       <c r="AE128" s="5" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="AF128" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG128" s="5" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="AH128" s="5">
         <v>1.4620299999999999</v>
@@ -10407,22 +10429,22 @@
       </c>
       <c r="AM128" s="5"/>
     </row>
-    <row r="129" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A129" s="5"/>
       <c r="B129" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D129" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G129" s="5"/>
       <c r="H129" s="5" t="s">
@@ -10437,7 +10459,7 @@
         <v>48</v>
       </c>
       <c r="M129" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N129" s="5"/>
       <c r="O129" s="5"/>
@@ -10469,13 +10491,13 @@
       <c r="AC129" s="5"/>
       <c r="AD129" s="5"/>
       <c r="AE129" s="5" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="AF129" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG129" s="5" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="AH129" s="5">
         <v>1.4620299999999999</v>
@@ -10494,22 +10516,22 @@
       </c>
       <c r="AM129" s="5"/>
     </row>
-    <row r="130" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A130" s="5"/>
       <c r="B130" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G130" s="5"/>
       <c r="H130" s="5" t="s">
@@ -10524,7 +10546,7 @@
         <v>54</v>
       </c>
       <c r="M130" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N130" s="5"/>
       <c r="O130" s="5"/>
@@ -10556,13 +10578,13 @@
       <c r="AC130" s="5"/>
       <c r="AD130" s="5"/>
       <c r="AE130" s="5" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="AF130" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG130" s="5" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="AH130" s="5">
         <v>1.4620299999999999</v>
@@ -10581,22 +10603,22 @@
       </c>
       <c r="AM130" s="5"/>
     </row>
-    <row r="131" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A131" s="5"/>
       <c r="B131" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D131" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G131" s="5"/>
       <c r="H131" s="5"/>
@@ -10650,22 +10672,22 @@
       <c r="AL131" s="5"/>
       <c r="AM131" s="5"/>
     </row>
-    <row r="132" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A132" s="5"/>
       <c r="B132" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D132" s="5" t="s">
         <v>74</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G132" s="5"/>
       <c r="H132" s="5"/>
@@ -10719,22 +10741,22 @@
       <c r="AL132" s="5"/>
       <c r="AM132" s="5"/>
     </row>
-    <row r="133" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A133" s="5"/>
       <c r="B133" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D133" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G133" s="5"/>
       <c r="H133" s="5" t="s">
@@ -10792,22 +10814,22 @@
       <c r="AL133" s="5"/>
       <c r="AM133" s="5"/>
     </row>
-    <row r="134" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A134" s="5"/>
       <c r="B134" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D134" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G134" s="5"/>
       <c r="H134" s="5" t="s">
@@ -10865,22 +10887,22 @@
       <c r="AL134" s="5"/>
       <c r="AM134" s="5"/>
     </row>
-    <row r="135" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A135" s="5"/>
       <c r="B135" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D135" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G135" s="5"/>
       <c r="H135" s="5" t="s">
@@ -10938,22 +10960,22 @@
       <c r="AL135" s="5"/>
       <c r="AM135" s="5"/>
     </row>
-    <row r="136" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A136" s="5"/>
       <c r="B136" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D136" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G136" s="5"/>
       <c r="H136" s="5" t="s">
@@ -11011,22 +11033,22 @@
       <c r="AL136" s="5"/>
       <c r="AM136" s="5"/>
     </row>
-    <row r="137" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A137" s="5"/>
       <c r="B137" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D137" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G137" s="5"/>
       <c r="H137" s="5"/>
@@ -11080,22 +11102,22 @@
       <c r="AL137" s="5"/>
       <c r="AM137" s="5"/>
     </row>
-    <row r="138" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A138" s="5"/>
       <c r="B138" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D138" s="5" t="s">
         <v>74</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G138" s="5"/>
       <c r="H138" s="5"/>
@@ -11149,22 +11171,22 @@
       <c r="AL138" s="5"/>
       <c r="AM138" s="5"/>
     </row>
-    <row r="139" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A139" s="5"/>
       <c r="B139" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G139" s="5"/>
       <c r="H139" s="5"/>
@@ -11218,22 +11240,22 @@
       <c r="AL139" s="5"/>
       <c r="AM139" s="5"/>
     </row>
-    <row r="140" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A140" s="5"/>
       <c r="B140" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="D140" s="5" t="s">
         <v>74</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G140" s="5"/>
       <c r="H140" s="5"/>
@@ -11287,22 +11309,22 @@
       <c r="AL140" s="5"/>
       <c r="AM140" s="5"/>
     </row>
-    <row r="141" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A141" s="5"/>
       <c r="B141" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G141" s="5"/>
       <c r="H141" s="5"/>
@@ -11356,22 +11378,22 @@
       <c r="AL141" s="5"/>
       <c r="AM141" s="5"/>
     </row>
-    <row r="142" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A142" s="5"/>
       <c r="B142" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D142" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G142" s="5"/>
       <c r="H142" s="5" t="s">
@@ -11386,7 +11408,7 @@
         <v>48</v>
       </c>
       <c r="M142" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N142" s="5"/>
       <c r="O142" s="5"/>
@@ -11418,13 +11440,13 @@
       <c r="AC142" s="5"/>
       <c r="AD142" s="5"/>
       <c r="AE142" s="5" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="AF142" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG142" s="5" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="AH142" s="5"/>
       <c r="AI142" s="5"/>
@@ -11439,22 +11461,22 @@
       </c>
       <c r="AM142" s="5"/>
     </row>
-    <row r="143" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A143" s="5"/>
       <c r="B143" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G143" s="5"/>
       <c r="H143" s="5" t="s">
@@ -11469,7 +11491,7 @@
         <v>54</v>
       </c>
       <c r="M143" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N143" s="5"/>
       <c r="O143" s="5"/>
@@ -11501,13 +11523,13 @@
       <c r="AC143" s="5"/>
       <c r="AD143" s="5"/>
       <c r="AE143" s="5" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="AF143" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG143" s="5" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="AH143" s="5"/>
       <c r="AI143" s="5"/>
@@ -11522,22 +11544,22 @@
       </c>
       <c r="AM143" s="5"/>
     </row>
-    <row r="144" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A144" s="5"/>
       <c r="B144" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D144" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G144" s="5"/>
       <c r="H144" s="5" t="s">
@@ -11552,7 +11574,7 @@
         <v>48</v>
       </c>
       <c r="M144" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N144" s="5"/>
       <c r="O144" s="5"/>
@@ -11584,13 +11606,13 @@
       <c r="AC144" s="5"/>
       <c r="AD144" s="5"/>
       <c r="AE144" s="5" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="AF144" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG144" s="5" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="AH144" s="5"/>
       <c r="AI144" s="5"/>
@@ -11605,22 +11627,22 @@
       </c>
       <c r="AM144" s="5"/>
     </row>
-    <row r="145" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A145" s="5"/>
       <c r="B145" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G145" s="5"/>
       <c r="H145" s="5" t="s">
@@ -11635,7 +11657,7 @@
         <v>54</v>
       </c>
       <c r="M145" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N145" s="5"/>
       <c r="O145" s="5"/>
@@ -11667,13 +11689,13 @@
       <c r="AC145" s="5"/>
       <c r="AD145" s="5"/>
       <c r="AE145" s="5" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="AF145" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG145" s="5" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="AH145" s="5"/>
       <c r="AI145" s="5"/>
@@ -11688,22 +11710,22 @@
       </c>
       <c r="AM145" s="5"/>
     </row>
-    <row r="146" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A146" s="5"/>
       <c r="B146" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D146" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G146" s="5"/>
       <c r="H146" s="5"/>
@@ -11757,22 +11779,22 @@
       <c r="AL146" s="5"/>
       <c r="AM146" s="5"/>
     </row>
-    <row r="147" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A147" s="5"/>
       <c r="B147" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D147" s="5" t="s">
         <v>74</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G147" s="5"/>
       <c r="H147" s="5"/>
@@ -11826,22 +11848,22 @@
       <c r="AL147" s="5"/>
       <c r="AM147" s="5"/>
     </row>
-    <row r="148" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A148" s="5"/>
       <c r="B148" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G148" s="5"/>
       <c r="H148" s="5"/>
@@ -11895,22 +11917,22 @@
       <c r="AL148" s="5"/>
       <c r="AM148" s="5"/>
     </row>
-    <row r="149" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A149" s="5"/>
       <c r="B149" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D149" s="5" t="s">
         <v>74</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G149" s="5"/>
       <c r="H149" s="5"/>

--- a/inst/extdata/ute_mountain_ute_tribe_criteria_crosswalk.xlsx
+++ b/inst/extdata/ute_mountain_ute_tribe_criteria_crosswalk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/sheila_saia_tetratech_com/Documents/Documents/github/TADACommunityHub/inst/extdata/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwong01\TADACommunityHub\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="13_ncr:1_{50F5F14F-865B-4854-927D-C8A959F1A688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A658DD2-E518-4588-81AA-8C5F3AD5E6FB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD9C856-9947-4DB5-A76E-1B8A8E6FBB4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0939A520-3B6D-499A-B5C0-4CEBC761A507}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0939A520-3B6D-499A-B5C0-4CEBC761A507}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -299,9 +299,6 @@
     <t>ESCHERICHIA COLI</t>
   </si>
   <si>
-    <t>#/100mL</t>
-  </si>
-  <si>
     <t>geometric mean</t>
   </si>
   <si>
@@ -534,6 +531,9 @@
   </si>
   <si>
     <t>(1.136672-In(hardness)*(0.041838))*e^(1.0166*(In(hardness))-3.924)</t>
+  </si>
+  <si>
+    <t>CFU/100ML</t>
   </si>
 </sst>
 </file>
@@ -943,14 +943,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5669769F-2254-4C2D-A5BA-32D6C5B999AC}">
   <dimension ref="A1:AP149"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="5"/>
-    <col min="2" max="2" width="29.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="5"/>
+    <col min="1" max="1" width="9.1796875" style="5"/>
+    <col min="2" max="2" width="29.81640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.1796875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:42" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1078,7 +1078,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
         <v>42</v>
@@ -1148,7 +1148,7 @@
       <c r="AK2" s="3"/>
       <c r="AL2" s="3"/>
     </row>
-    <row r="3" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
         <v>42</v>
@@ -1218,7 +1218,7 @@
       <c r="AK3" s="3"/>
       <c r="AL3" s="3"/>
     </row>
-    <row r="4" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
         <v>42</v>
@@ -1286,7 +1286,7 @@
       <c r="AK4" s="3"/>
       <c r="AL4" s="3"/>
     </row>
-    <row r="5" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
         <v>42</v>
@@ -1354,7 +1354,7 @@
       <c r="AK5" s="3"/>
       <c r="AL5" s="3"/>
     </row>
-    <row r="6" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
         <v>42</v>
@@ -1422,7 +1422,7 @@
       <c r="AK6" s="3"/>
       <c r="AL6" s="3"/>
     </row>
-    <row r="7" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
         <v>42</v>
@@ -1490,13 +1490,13 @@
       <c r="AK7" s="3"/>
       <c r="AL7" s="3"/>
     </row>
-    <row r="8" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>57</v>
@@ -1558,13 +1558,13 @@
       <c r="AK8" s="3"/>
       <c r="AL8" s="3"/>
     </row>
-    <row r="9" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>57</v>
@@ -1628,13 +1628,13 @@
       <c r="AK9" s="3"/>
       <c r="AL9" s="3"/>
     </row>
-    <row r="10" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>57</v>
@@ -1696,13 +1696,13 @@
       <c r="AK10" s="3"/>
       <c r="AL10" s="3"/>
     </row>
-    <row r="11" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>57</v>
@@ -1764,13 +1764,13 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>57</v>
@@ -1832,13 +1832,13 @@
       <c r="AK12" s="3"/>
       <c r="AL12" s="3"/>
     </row>
-    <row r="13" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>57</v>
@@ -1900,13 +1900,13 @@
       <c r="AK13" s="3"/>
       <c r="AL13" s="3"/>
     </row>
-    <row r="14" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>57</v>
@@ -1968,7 +1968,7 @@
       <c r="AK14" s="3"/>
       <c r="AL14" s="3"/>
     </row>
-    <row r="15" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
         <v>42</v>
@@ -2036,7 +2036,7 @@
       <c r="AK15" s="3"/>
       <c r="AL15" s="3"/>
     </row>
-    <row r="16" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
         <v>42</v>
@@ -2104,7 +2104,7 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
         <v>42</v>
@@ -2172,7 +2172,7 @@
       <c r="AK17" s="3"/>
       <c r="AL17" s="3"/>
     </row>
-    <row r="18" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
         <v>42</v>
@@ -2240,7 +2240,7 @@
       <c r="AK18" s="3"/>
       <c r="AL18" s="3"/>
     </row>
-    <row r="19" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
         <v>42</v>
@@ -2308,13 +2308,13 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>44</v>
@@ -2378,13 +2378,13 @@
       <c r="AK20" s="3"/>
       <c r="AL20" s="3"/>
     </row>
-    <row r="21" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>44</v>
@@ -2448,13 +2448,13 @@
       <c r="AK21" s="3"/>
       <c r="AL21" s="3"/>
     </row>
-    <row r="22" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>44</v>
@@ -2518,13 +2518,13 @@
       <c r="AK22" s="3"/>
       <c r="AL22" s="3"/>
     </row>
-    <row r="23" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>44</v>
@@ -2588,13 +2588,13 @@
       <c r="AK23" s="3"/>
       <c r="AL23" s="3"/>
     </row>
-    <row r="24" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>44</v>
@@ -2658,13 +2658,13 @@
       <c r="AK24" s="3"/>
       <c r="AL24" s="3"/>
     </row>
-    <row r="25" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>44</v>
@@ -2728,13 +2728,13 @@
       <c r="AK25" s="3"/>
       <c r="AL25" s="3"/>
     </row>
-    <row r="26" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>44</v>
@@ -2798,13 +2798,13 @@
       <c r="AK26" s="3"/>
       <c r="AL26" s="3"/>
     </row>
-    <row r="27" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>44</v>
@@ -2868,13 +2868,13 @@
       <c r="AK27" s="3"/>
       <c r="AL27" s="3"/>
     </row>
-    <row r="28" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>44</v>
@@ -2938,13 +2938,13 @@
       <c r="AK28" s="3"/>
       <c r="AL28" s="3"/>
     </row>
-    <row r="29" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>44</v>
@@ -3008,13 +3008,13 @@
       <c r="AK29" s="3"/>
       <c r="AL29" s="3"/>
     </row>
-    <row r="30" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>54</v>
@@ -3039,7 +3039,7 @@
         <v>126</v>
       </c>
       <c r="P30" s="3" t="s">
-        <v>87</v>
+        <v>165</v>
       </c>
       <c r="Q30" s="3">
         <v>1</v>
@@ -3048,7 +3048,7 @@
         <v>50</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="T30" s="3">
         <v>1</v>
@@ -3074,13 +3074,13 @@
       <c r="AK30" s="3"/>
       <c r="AL30" s="3"/>
     </row>
-    <row r="31" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>54</v>
@@ -3105,7 +3105,7 @@
         <v>235</v>
       </c>
       <c r="P31" s="3" t="s">
-        <v>87</v>
+        <v>165</v>
       </c>
       <c r="Q31" s="3">
         <v>1</v>
@@ -3140,13 +3140,13 @@
       <c r="AK31" s="3"/>
       <c r="AL31" s="3"/>
     </row>
-    <row r="32" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>55</v>
@@ -3171,7 +3171,7 @@
         <v>1152</v>
       </c>
       <c r="P32" s="3" t="s">
-        <v>87</v>
+        <v>165</v>
       </c>
       <c r="Q32" s="3">
         <v>1</v>
@@ -3206,13 +3206,13 @@
       <c r="AK32" s="3"/>
       <c r="AL32" s="3"/>
     </row>
-    <row r="33" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>44</v>
@@ -3234,7 +3234,7 @@
         <v>47</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N33" s="3"/>
       <c r="O33" s="3"/>
@@ -3269,7 +3269,7 @@
         <v>43</v>
       </c>
       <c r="AF33" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AG33" s="3"/>
       <c r="AH33" s="3"/>
@@ -3290,16 +3290,16 @@
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="34" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>58</v>
@@ -3318,7 +3318,7 @@
         <v>53</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N34" s="3"/>
       <c r="O34" s="3"/>
@@ -3353,7 +3353,7 @@
         <v>43</v>
       </c>
       <c r="AF34" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AG34" s="3"/>
       <c r="AH34" s="3"/>
@@ -3374,13 +3374,13 @@
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="35" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>44</v>
@@ -3402,7 +3402,7 @@
         <v>47</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N35" s="3"/>
       <c r="O35" s="3"/>
@@ -3434,10 +3434,10 @@
       <c r="AC35" s="3"/>
       <c r="AD35" s="3"/>
       <c r="AE35" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AF35" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="AF35" s="3" t="s">
-        <v>94</v>
       </c>
       <c r="AG35" s="3"/>
       <c r="AH35" s="3"/>
@@ -3446,16 +3446,16 @@
       <c r="AK35" s="3"/>
       <c r="AL35" s="3"/>
     </row>
-    <row r="36" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>58</v>
@@ -3474,7 +3474,7 @@
         <v>53</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N36" s="3"/>
       <c r="O36" s="3"/>
@@ -3506,10 +3506,10 @@
       <c r="AC36" s="3"/>
       <c r="AD36" s="3"/>
       <c r="AE36" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AF36" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="AF36" s="3" t="s">
-        <v>94</v>
       </c>
       <c r="AG36" s="3"/>
       <c r="AH36" s="3"/>
@@ -3518,13 +3518,13 @@
       <c r="AK36" s="3"/>
       <c r="AL36" s="3"/>
     </row>
-    <row r="37" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>44</v>
@@ -3543,10 +3543,10 @@
       </c>
       <c r="K37" s="3"/>
       <c r="L37" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N37" s="3"/>
       <c r="O37" s="3"/>
@@ -3581,7 +3581,7 @@
         <v>43</v>
       </c>
       <c r="AF37" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AG37" s="3"/>
       <c r="AH37" s="3"/>
@@ -3602,16 +3602,16 @@
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>58</v>
@@ -3627,10 +3627,10 @@
       </c>
       <c r="K38" s="3"/>
       <c r="L38" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N38" s="3"/>
       <c r="O38" s="3"/>
@@ -3665,7 +3665,7 @@
         <v>43</v>
       </c>
       <c r="AF38" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AG38" s="3"/>
       <c r="AH38" s="3"/>
@@ -3686,13 +3686,13 @@
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>44</v>
@@ -3711,10 +3711,10 @@
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
@@ -3746,10 +3746,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AF39" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
@@ -3758,16 +3758,16 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A40" s="3"/>
       <c r="B40" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>58</v>
@@ -3783,10 +3783,10 @@
       </c>
       <c r="K40" s="3"/>
       <c r="L40" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
@@ -3818,10 +3818,10 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AF40" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
@@ -3830,13 +3830,13 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="3"/>
       <c r="B41" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>73</v>
@@ -3898,13 +3898,13 @@
       <c r="AK41" s="3"/>
       <c r="AL41" s="3"/>
     </row>
-    <row r="42" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" s="3"/>
       <c r="B42" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>44</v>
@@ -3970,13 +3970,13 @@
       <c r="AK42" s="3"/>
       <c r="AL42" s="3"/>
     </row>
-    <row r="43" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>44</v>
@@ -4042,13 +4042,13 @@
       <c r="AK43" s="3"/>
       <c r="AL43" s="3"/>
     </row>
-    <row r="44" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>44</v>
@@ -4114,13 +4114,13 @@
       <c r="AK44" s="3"/>
       <c r="AL44" s="3"/>
     </row>
-    <row r="45" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="3"/>
       <c r="B45" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>44</v>
@@ -4186,13 +4186,13 @@
       <c r="AK45" s="3"/>
       <c r="AL45" s="3"/>
     </row>
-    <row r="46" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" s="3"/>
       <c r="B46" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>73</v>
@@ -4256,13 +4256,13 @@
       <c r="AK46" s="3"/>
       <c r="AL46" s="3"/>
     </row>
-    <row r="47" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="3"/>
       <c r="B47" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>44</v>
@@ -4284,7 +4284,7 @@
         <v>47</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N47" s="3"/>
       <c r="O47" s="3"/>
@@ -4316,10 +4316,10 @@
       <c r="AC47" s="3"/>
       <c r="AD47" s="3"/>
       <c r="AE47" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AF47" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AG47" s="3"/>
       <c r="AH47" s="3"/>
@@ -4328,16 +4328,16 @@
       <c r="AK47" s="3"/>
       <c r="AL47" s="3"/>
     </row>
-    <row r="48" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" s="3"/>
       <c r="B48" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>67</v>
@@ -4356,7 +4356,7 @@
         <v>53</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" s="3"/>
@@ -4388,10 +4388,10 @@
       <c r="AC48" s="3"/>
       <c r="AD48" s="3"/>
       <c r="AE48" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AF48" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AG48" s="3"/>
       <c r="AH48" s="3"/>
@@ -4400,13 +4400,13 @@
       <c r="AK48" s="3"/>
       <c r="AL48" s="3"/>
     </row>
-    <row r="49" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="3"/>
       <c r="B49" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>44</v>
@@ -4428,7 +4428,7 @@
         <v>47</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N49" s="3"/>
       <c r="O49" s="3"/>
@@ -4460,10 +4460,10 @@
       <c r="AC49" s="3"/>
       <c r="AD49" s="3"/>
       <c r="AE49" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AF49" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AG49" s="3"/>
       <c r="AH49" s="3"/>
@@ -4472,16 +4472,16 @@
       <c r="AK49" s="3"/>
       <c r="AL49" s="3"/>
     </row>
-    <row r="50" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" s="3"/>
       <c r="B50" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>67</v>
@@ -4500,7 +4500,7 @@
         <v>53</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N50" s="3"/>
       <c r="O50" s="3"/>
@@ -4532,10 +4532,10 @@
       <c r="AC50" s="3"/>
       <c r="AD50" s="3"/>
       <c r="AE50" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AF50" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AG50" s="3"/>
       <c r="AH50" s="3"/>
@@ -4544,13 +4544,13 @@
       <c r="AK50" s="3"/>
       <c r="AL50" s="3"/>
     </row>
-    <row r="51" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51" s="3"/>
       <c r="B51" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>56</v>
@@ -4612,13 +4612,13 @@
       <c r="AK51" s="3"/>
       <c r="AL51" s="3"/>
     </row>
-    <row r="52" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" s="3"/>
       <c r="B52" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>56</v>
@@ -4680,13 +4680,13 @@
       <c r="AK52" s="3"/>
       <c r="AL52" s="3"/>
     </row>
-    <row r="53" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" s="3"/>
       <c r="B53" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>73</v>
@@ -4748,13 +4748,13 @@
       <c r="AK53" s="3"/>
       <c r="AL53" s="3"/>
     </row>
-    <row r="54" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A54" s="3"/>
       <c r="B54" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>73</v>
@@ -4816,13 +4816,13 @@
       <c r="AK54" s="3"/>
       <c r="AL54" s="3"/>
     </row>
-    <row r="55" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A55" s="3"/>
       <c r="B55" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>44</v>
@@ -4886,13 +4886,13 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A56" s="3"/>
       <c r="B56" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>44</v>
@@ -4956,13 +4956,13 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A57" s="3"/>
       <c r="B57" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>44</v>
@@ -5026,13 +5026,13 @@
       <c r="AK57" s="3"/>
       <c r="AL57" s="3"/>
     </row>
-    <row r="58" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A58" s="3"/>
       <c r="B58" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>44</v>
@@ -5096,13 +5096,13 @@
       <c r="AK58" s="3"/>
       <c r="AL58" s="3"/>
     </row>
-    <row r="59" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A59" s="3"/>
       <c r="B59" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>56</v>
@@ -5164,13 +5164,13 @@
       <c r="AK59" s="3"/>
       <c r="AL59" s="3"/>
     </row>
-    <row r="60" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A60" s="3"/>
       <c r="B60" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>73</v>
@@ -5232,19 +5232,19 @@
       <c r="AK60" s="3"/>
       <c r="AL60" s="3"/>
     </row>
-    <row r="61" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A61" s="3"/>
       <c r="B61" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3"/>
@@ -5300,13 +5300,13 @@
       <c r="AK61" s="3"/>
       <c r="AL61" s="3"/>
     </row>
-    <row r="62" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A62" s="3"/>
       <c r="B62" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>44</v>
@@ -5370,13 +5370,13 @@
       <c r="AK62" s="3"/>
       <c r="AL62" s="3"/>
     </row>
-    <row r="63" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A63" s="3"/>
       <c r="B63" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>44</v>
@@ -5440,13 +5440,13 @@
       <c r="AK63" s="3"/>
       <c r="AL63" s="3"/>
     </row>
-    <row r="64" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A64" s="3"/>
       <c r="B64" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>73</v>
@@ -5508,13 +5508,13 @@
       <c r="AK64" s="3"/>
       <c r="AL64" s="3"/>
     </row>
-    <row r="65" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A65" s="3"/>
       <c r="B65" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>73</v>
@@ -5576,19 +5576,19 @@
       <c r="AK65" s="3"/>
       <c r="AL65" s="3"/>
     </row>
-    <row r="66" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A66" s="3"/>
       <c r="B66" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>79</v>
@@ -5606,7 +5606,7 @@
         <v>47</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N66" s="3"/>
       <c r="O66" s="3"/>
@@ -5638,10 +5638,10 @@
       <c r="AC66" s="3"/>
       <c r="AD66" s="3"/>
       <c r="AE66" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF66" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AG66" s="3"/>
       <c r="AH66" s="3"/>
@@ -5656,19 +5656,19 @@
       </c>
       <c r="AL66" s="3"/>
     </row>
-    <row r="67" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A67" s="3"/>
       <c r="B67" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C67" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E67" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>110</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>79</v>
@@ -5686,7 +5686,7 @@
         <v>53</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
@@ -5718,10 +5718,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF67" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
@@ -5736,19 +5736,19 @@
       </c>
       <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A68" s="3"/>
       <c r="B68" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>79</v>
@@ -5766,7 +5766,7 @@
         <v>47</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N68" s="3"/>
       <c r="O68" s="3"/>
@@ -5798,10 +5798,10 @@
       <c r="AC68" s="3"/>
       <c r="AD68" s="3"/>
       <c r="AE68" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF68" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG68" s="3"/>
       <c r="AH68" s="3"/>
@@ -5816,19 +5816,19 @@
       </c>
       <c r="AL68" s="3"/>
     </row>
-    <row r="69" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A69" s="3"/>
       <c r="B69" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C69" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E69" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>110</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>79</v>
@@ -5846,7 +5846,7 @@
         <v>53</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N69" s="3"/>
       <c r="O69" s="3"/>
@@ -5878,10 +5878,10 @@
       <c r="AC69" s="3"/>
       <c r="AD69" s="3"/>
       <c r="AE69" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF69" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AG69" s="3"/>
       <c r="AH69" s="3"/>
@@ -5896,22 +5896,22 @@
       </c>
       <c r="AL69" s="3"/>
     </row>
-    <row r="70" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A70" s="3"/>
       <c r="B70" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>73</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G70" s="3"/>
       <c r="H70" s="3"/>
@@ -5964,22 +5964,22 @@
       <c r="AK70" s="3"/>
       <c r="AL70" s="3"/>
     </row>
-    <row r="71" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A71" s="3"/>
       <c r="B71" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C71" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E71" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D71" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="E71" s="3" t="s">
-        <v>110</v>
-      </c>
       <c r="F71" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G71" s="3"/>
       <c r="H71" s="3"/>
@@ -6032,22 +6032,22 @@
       <c r="AK71" s="3"/>
       <c r="AL71" s="3"/>
     </row>
-    <row r="72" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A72" s="3"/>
       <c r="B72" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G72" s="3"/>
       <c r="H72" s="3" t="s">
@@ -6104,22 +6104,22 @@
       <c r="AK72" s="3"/>
       <c r="AL72" s="3"/>
     </row>
-    <row r="73" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A73" s="3"/>
       <c r="B73" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G73" s="3"/>
       <c r="H73" s="3" t="s">
@@ -6176,22 +6176,22 @@
       <c r="AK73" s="3"/>
       <c r="AL73" s="3"/>
     </row>
-    <row r="74" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A74" s="3"/>
       <c r="B74" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G74" s="3"/>
       <c r="H74" s="3" t="s">
@@ -6248,22 +6248,22 @@
       <c r="AK74" s="3"/>
       <c r="AL74" s="3"/>
     </row>
-    <row r="75" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A75" s="3"/>
       <c r="B75" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G75" s="3"/>
       <c r="H75" s="3" t="s">
@@ -6320,22 +6320,22 @@
       <c r="AK75" s="3"/>
       <c r="AL75" s="3"/>
     </row>
-    <row r="76" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A76" s="3"/>
       <c r="B76" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>73</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G76" s="3"/>
       <c r="H76" s="3"/>
@@ -6388,22 +6388,22 @@
       <c r="AK76" s="3"/>
       <c r="AL76" s="3"/>
     </row>
-    <row r="77" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A77" s="3"/>
       <c r="B77" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G77" s="3"/>
       <c r="H77" s="3" t="s">
@@ -6458,22 +6458,22 @@
       <c r="AK77" s="3"/>
       <c r="AL77" s="3"/>
     </row>
-    <row r="78" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A78" s="3"/>
       <c r="B78" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G78" s="3"/>
       <c r="H78" s="3" t="s">
@@ -6530,22 +6530,22 @@
       <c r="AK78" s="3"/>
       <c r="AL78" s="3"/>
     </row>
-    <row r="79" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A79" s="3"/>
       <c r="B79" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G79" s="3"/>
       <c r="H79" s="3" t="s">
@@ -6602,22 +6602,22 @@
       <c r="AK79" s="3"/>
       <c r="AL79" s="3"/>
     </row>
-    <row r="80" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A80" s="3"/>
       <c r="B80" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G80" s="3"/>
       <c r="H80" s="3" t="s">
@@ -6674,22 +6674,22 @@
       <c r="AK80" s="3"/>
       <c r="AL80" s="3"/>
     </row>
-    <row r="81" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A81" s="3"/>
       <c r="B81" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G81" s="3"/>
       <c r="H81" s="3"/>
@@ -6742,22 +6742,22 @@
       <c r="AK81" s="3"/>
       <c r="AL81" s="3"/>
     </row>
-    <row r="82" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A82" s="3"/>
       <c r="B82" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>73</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G82" s="3"/>
       <c r="H82" s="3"/>
@@ -6810,22 +6810,22 @@
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A83" s="3"/>
       <c r="B83" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C83" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E83" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>117</v>
-      </c>
       <c r="F83" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G83" s="3"/>
       <c r="H83" s="3"/>
@@ -6878,22 +6878,22 @@
       <c r="AK83" s="3"/>
       <c r="AL83" s="3"/>
     </row>
-    <row r="84" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A84" s="3"/>
       <c r="B84" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>73</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G84" s="3"/>
       <c r="H84" s="3"/>
@@ -6903,7 +6903,7 @@
       </c>
       <c r="K84" s="3"/>
       <c r="L84" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M84" s="3" t="s">
         <v>48</v>
@@ -6948,19 +6948,19 @@
       <c r="AK84" s="3"/>
       <c r="AL84" s="3"/>
     </row>
-    <row r="85" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A85" s="3"/>
       <c r="B85" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>79</v>
@@ -6978,7 +6978,7 @@
         <v>47</v>
       </c>
       <c r="M85" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N85" s="3"/>
       <c r="O85" s="3"/>
@@ -7010,10 +7010,10 @@
       <c r="AC85" s="3"/>
       <c r="AD85" s="3"/>
       <c r="AE85" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF85" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AG85" s="3">
         <v>1.1366719999999999</v>
@@ -7032,19 +7032,19 @@
       </c>
       <c r="AL85" s="3"/>
     </row>
-    <row r="86" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A86" s="3"/>
       <c r="B86" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C86" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E86" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>122</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>79</v>
@@ -7062,7 +7062,7 @@
         <v>53</v>
       </c>
       <c r="M86" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N86" s="3"/>
       <c r="O86" s="3"/>
@@ -7094,10 +7094,10 @@
       <c r="AC86" s="3"/>
       <c r="AD86" s="3"/>
       <c r="AE86" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF86" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AG86" s="3">
         <v>1.1366719999999999</v>
@@ -7116,19 +7116,19 @@
       </c>
       <c r="AL86" s="3"/>
     </row>
-    <row r="87" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A87" s="3"/>
       <c r="B87" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>79</v>
@@ -7146,7 +7146,7 @@
         <v>47</v>
       </c>
       <c r="M87" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N87" s="3"/>
       <c r="O87" s="3"/>
@@ -7178,10 +7178,10 @@
       <c r="AC87" s="3"/>
       <c r="AD87" s="3"/>
       <c r="AE87" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF87" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AG87" s="3">
         <v>1.101672</v>
@@ -7200,19 +7200,19 @@
       </c>
       <c r="AL87" s="3"/>
     </row>
-    <row r="88" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A88" s="3"/>
       <c r="B88" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C88" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E88" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>122</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>79</v>
@@ -7230,7 +7230,7 @@
         <v>53</v>
       </c>
       <c r="M88" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N88" s="3"/>
       <c r="O88" s="3"/>
@@ -7262,10 +7262,10 @@
       <c r="AC88" s="3"/>
       <c r="AD88" s="3"/>
       <c r="AE88" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF88" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AG88" s="3">
         <v>1.101672</v>
@@ -7284,22 +7284,22 @@
       </c>
       <c r="AL88" s="3"/>
     </row>
-    <row r="89" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A89" s="3"/>
       <c r="B89" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G89" s="3"/>
       <c r="H89" s="3"/>
@@ -7352,22 +7352,22 @@
       <c r="AK89" s="3"/>
       <c r="AL89" s="3"/>
     </row>
-    <row r="90" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A90" s="3"/>
       <c r="B90" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>73</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G90" s="3"/>
       <c r="H90" s="3"/>
@@ -7420,22 +7420,22 @@
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A91" s="3"/>
       <c r="B91" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C91" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E91" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="F91" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G91" s="3"/>
       <c r="H91" s="3"/>
@@ -7488,19 +7488,19 @@
       <c r="AK91" s="3"/>
       <c r="AL91" s="3"/>
     </row>
-    <row r="92" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A92" s="3"/>
       <c r="B92" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>79</v>
@@ -7518,7 +7518,7 @@
         <v>47</v>
       </c>
       <c r="M92" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N92" s="3"/>
       <c r="O92" s="3"/>
@@ -7550,10 +7550,10 @@
       <c r="AC92" s="3"/>
       <c r="AD92" s="3"/>
       <c r="AE92" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF92" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AG92" s="3"/>
       <c r="AH92" s="3"/>
@@ -7568,19 +7568,19 @@
       </c>
       <c r="AL92" s="3"/>
     </row>
-    <row r="93" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A93" s="3"/>
       <c r="B93" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>79</v>
@@ -7598,7 +7598,7 @@
         <v>53</v>
       </c>
       <c r="M93" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N93" s="3"/>
       <c r="O93" s="3"/>
@@ -7630,10 +7630,10 @@
       <c r="AC93" s="3"/>
       <c r="AD93" s="3"/>
       <c r="AE93" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF93" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AG93" s="3"/>
       <c r="AH93" s="3"/>
@@ -7648,19 +7648,19 @@
       </c>
       <c r="AL93" s="3"/>
     </row>
-    <row r="94" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A94" s="3"/>
       <c r="B94" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>79</v>
@@ -7678,7 +7678,7 @@
         <v>47</v>
       </c>
       <c r="M94" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N94" s="3"/>
       <c r="O94" s="3"/>
@@ -7710,10 +7710,10 @@
       <c r="AC94" s="3"/>
       <c r="AD94" s="3"/>
       <c r="AE94" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF94" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AG94" s="3"/>
       <c r="AH94" s="3"/>
@@ -7728,19 +7728,19 @@
       </c>
       <c r="AL94" s="3"/>
     </row>
-    <row r="95" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A95" s="3"/>
       <c r="B95" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>79</v>
@@ -7758,7 +7758,7 @@
         <v>53</v>
       </c>
       <c r="M95" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
@@ -7790,10 +7790,10 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF95" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
@@ -7808,22 +7808,22 @@
       </c>
       <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A96" s="3"/>
       <c r="B96" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G96" s="3"/>
       <c r="H96" s="3"/>
@@ -7876,22 +7876,22 @@
       <c r="AK96" s="3"/>
       <c r="AL96" s="3"/>
     </row>
-    <row r="97" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A97" s="3"/>
       <c r="B97" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>73</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G97" s="3"/>
       <c r="H97" s="3"/>
@@ -7944,22 +7944,22 @@
       <c r="AK97" s="3"/>
       <c r="AL97" s="3"/>
     </row>
-    <row r="98" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A98" s="3"/>
       <c r="B98" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G98" s="3"/>
       <c r="H98" s="3"/>
@@ -8012,19 +8012,19 @@
       <c r="AK98" s="3"/>
       <c r="AL98" s="3"/>
     </row>
-    <row r="99" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A99" s="3"/>
       <c r="B99" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>79</v>
@@ -8084,19 +8084,19 @@
       <c r="AK99" s="3"/>
       <c r="AL99" s="3"/>
     </row>
-    <row r="100" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A100" s="3"/>
       <c r="B100" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>79</v>
@@ -8156,19 +8156,19 @@
       <c r="AK100" s="3"/>
       <c r="AL100" s="3"/>
     </row>
-    <row r="101" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A101" s="3"/>
       <c r="B101" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>79</v>
@@ -8228,19 +8228,19 @@
       <c r="AK101" s="3"/>
       <c r="AL101" s="3"/>
     </row>
-    <row r="102" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A102" s="3"/>
       <c r="B102" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>79</v>
@@ -8300,22 +8300,22 @@
       <c r="AK102" s="3"/>
       <c r="AL102" s="3"/>
     </row>
-    <row r="103" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A103" s="3"/>
       <c r="B103" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D103" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G103" s="3"/>
       <c r="H103" s="3"/>
@@ -8368,22 +8368,22 @@
       <c r="AK103" s="3"/>
       <c r="AL103" s="3"/>
     </row>
-    <row r="104" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A104" s="3"/>
       <c r="B104" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>73</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G104" s="3"/>
       <c r="H104" s="3"/>
@@ -8436,22 +8436,22 @@
       <c r="AK104" s="3"/>
       <c r="AL104" s="3"/>
     </row>
-    <row r="105" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A105" s="3"/>
       <c r="B105" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G105" s="3"/>
       <c r="H105" s="3"/>
@@ -8504,19 +8504,19 @@
       <c r="AK105" s="3"/>
       <c r="AL105" s="3"/>
     </row>
-    <row r="106" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A106" s="3"/>
       <c r="B106" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>79</v>
@@ -8534,7 +8534,7 @@
         <v>47</v>
       </c>
       <c r="M106" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N106" s="3"/>
       <c r="O106" s="3"/>
@@ -8566,10 +8566,10 @@
       <c r="AC106" s="3"/>
       <c r="AD106" s="3"/>
       <c r="AE106" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF106" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AG106" s="3"/>
       <c r="AH106" s="3"/>
@@ -8584,19 +8584,19 @@
       </c>
       <c r="AL106" s="3"/>
     </row>
-    <row r="107" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A107" s="3"/>
       <c r="B107" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C107" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E107" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="D107" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E107" s="3" t="s">
-        <v>126</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>79</v>
@@ -8614,7 +8614,7 @@
         <v>53</v>
       </c>
       <c r="M107" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N107" s="3"/>
       <c r="O107" s="3"/>
@@ -8646,10 +8646,10 @@
       <c r="AC107" s="3"/>
       <c r="AD107" s="3"/>
       <c r="AE107" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF107" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AG107" s="3"/>
       <c r="AH107" s="3"/>
@@ -8664,19 +8664,19 @@
       </c>
       <c r="AL107" s="3"/>
     </row>
-    <row r="108" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A108" s="3"/>
       <c r="B108" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D108" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F108" s="3" t="s">
         <v>79</v>
@@ -8694,7 +8694,7 @@
         <v>47</v>
       </c>
       <c r="M108" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N108" s="3"/>
       <c r="O108" s="3"/>
@@ -8726,10 +8726,10 @@
       <c r="AC108" s="3"/>
       <c r="AD108" s="3"/>
       <c r="AE108" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF108" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AG108" s="3"/>
       <c r="AH108" s="3"/>
@@ -8744,19 +8744,19 @@
       </c>
       <c r="AL108" s="3"/>
     </row>
-    <row r="109" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A109" s="3"/>
       <c r="B109" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C109" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E109" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="D109" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E109" s="3" t="s">
-        <v>126</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>79</v>
@@ -8774,7 +8774,7 @@
         <v>53</v>
       </c>
       <c r="M109" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N109" s="3"/>
       <c r="O109" s="3"/>
@@ -8806,10 +8806,10 @@
       <c r="AC109" s="3"/>
       <c r="AD109" s="3"/>
       <c r="AE109" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF109" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AG109" s="3"/>
       <c r="AH109" s="3"/>
@@ -8824,22 +8824,22 @@
       </c>
       <c r="AL109" s="3"/>
     </row>
-    <row r="110" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A110" s="3"/>
       <c r="B110" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G110" s="3"/>
       <c r="H110" s="3"/>
@@ -8892,22 +8892,22 @@
       <c r="AK110" s="3"/>
       <c r="AL110" s="3"/>
     </row>
-    <row r="111" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A111" s="3"/>
       <c r="B111" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D111" s="3" t="s">
         <v>73</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G111" s="3"/>
       <c r="H111" s="3"/>
@@ -8960,22 +8960,22 @@
       <c r="AK111" s="3"/>
       <c r="AL111" s="3"/>
     </row>
-    <row r="112" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A112" s="3"/>
       <c r="B112" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D112" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G112" s="3"/>
       <c r="H112" s="3" t="s">
@@ -9032,22 +9032,22 @@
       <c r="AK112" s="3"/>
       <c r="AL112" s="3"/>
     </row>
-    <row r="113" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A113" s="3"/>
       <c r="B113" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D113" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G113" s="3"/>
       <c r="H113" s="3" t="s">
@@ -9104,22 +9104,22 @@
       <c r="AK113" s="3"/>
       <c r="AL113" s="3"/>
     </row>
-    <row r="114" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A114" s="3"/>
       <c r="B114" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D114" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G114" s="3"/>
       <c r="H114" s="3" t="s">
@@ -9176,22 +9176,22 @@
       <c r="AK114" s="3"/>
       <c r="AL114" s="3"/>
     </row>
-    <row r="115" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A115" s="3"/>
       <c r="B115" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D115" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G115" s="3"/>
       <c r="H115" s="3" t="s">
@@ -9248,22 +9248,22 @@
       <c r="AK115" s="3"/>
       <c r="AL115" s="3"/>
     </row>
-    <row r="116" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A116" s="3"/>
       <c r="B116" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D116" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G116" s="3"/>
       <c r="H116" s="3"/>
@@ -9316,22 +9316,22 @@
       <c r="AK116" s="3"/>
       <c r="AL116" s="3"/>
     </row>
-    <row r="117" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A117" s="3"/>
       <c r="B117" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D117" s="3" t="s">
         <v>73</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G117" s="3"/>
       <c r="H117" s="3"/>
@@ -9384,22 +9384,22 @@
       <c r="AK117" s="3"/>
       <c r="AL117" s="3"/>
     </row>
-    <row r="118" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A118" s="3"/>
       <c r="B118" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C118" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E118" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D118" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="E118" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="F118" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G118" s="3"/>
       <c r="H118" s="3"/>
@@ -9452,22 +9452,22 @@
       <c r="AK118" s="3"/>
       <c r="AL118" s="3"/>
     </row>
-    <row r="119" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A119" s="3"/>
       <c r="B119" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G119" s="3"/>
       <c r="H119" s="3"/>
@@ -9485,7 +9485,7 @@
         <v>0.3</v>
       </c>
       <c r="P119" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q119" s="3">
         <v>30</v>
@@ -9520,19 +9520,19 @@
       <c r="AK119" s="3"/>
       <c r="AL119" s="3"/>
     </row>
-    <row r="120" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A120" s="3"/>
       <c r="B120" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D120" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>79</v>
@@ -9550,7 +9550,7 @@
         <v>47</v>
       </c>
       <c r="M120" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N120" s="3"/>
       <c r="O120" s="3"/>
@@ -9582,10 +9582,10 @@
       <c r="AC120" s="3"/>
       <c r="AD120" s="3"/>
       <c r="AE120" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF120" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG120" s="3"/>
       <c r="AH120" s="3"/>
@@ -9600,19 +9600,19 @@
       </c>
       <c r="AL120" s="3"/>
     </row>
-    <row r="121" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A121" s="3"/>
       <c r="B121" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C121" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E121" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="D121" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>132</v>
       </c>
       <c r="F121" s="3" t="s">
         <v>79</v>
@@ -9630,7 +9630,7 @@
         <v>53</v>
       </c>
       <c r="M121" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N121" s="3"/>
       <c r="O121" s="3"/>
@@ -9662,10 +9662,10 @@
       <c r="AC121" s="3"/>
       <c r="AD121" s="3"/>
       <c r="AE121" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF121" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG121" s="3"/>
       <c r="AH121" s="3"/>
@@ -9680,19 +9680,19 @@
       </c>
       <c r="AL121" s="3"/>
     </row>
-    <row r="122" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A122" s="3"/>
       <c r="B122" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D122" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>79</v>
@@ -9710,7 +9710,7 @@
         <v>47</v>
       </c>
       <c r="M122" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N122" s="3"/>
       <c r="O122" s="3"/>
@@ -9742,10 +9742,10 @@
       <c r="AC122" s="3"/>
       <c r="AD122" s="3"/>
       <c r="AE122" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF122" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AG122" s="3"/>
       <c r="AH122" s="3"/>
@@ -9760,19 +9760,19 @@
       </c>
       <c r="AL122" s="3"/>
     </row>
-    <row r="123" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A123" s="3"/>
       <c r="B123" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C123" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E123" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="D123" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E123" s="3" t="s">
-        <v>132</v>
       </c>
       <c r="F123" s="3" t="s">
         <v>79</v>
@@ -9790,7 +9790,7 @@
         <v>53</v>
       </c>
       <c r="M123" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N123" s="3"/>
       <c r="O123" s="3"/>
@@ -9822,10 +9822,10 @@
       <c r="AC123" s="3"/>
       <c r="AD123" s="3"/>
       <c r="AE123" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF123" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AG123" s="3"/>
       <c r="AH123" s="3"/>
@@ -9840,22 +9840,22 @@
       </c>
       <c r="AL123" s="3"/>
     </row>
-    <row r="124" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A124" s="3"/>
       <c r="B124" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D124" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G124" s="3"/>
       <c r="H124" s="3"/>
@@ -9908,22 +9908,22 @@
       <c r="AK124" s="3"/>
       <c r="AL124" s="3"/>
     </row>
-    <row r="125" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A125" s="3"/>
       <c r="B125" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D125" s="3" t="s">
         <v>73</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G125" s="3"/>
       <c r="H125" s="3"/>
@@ -9976,22 +9976,22 @@
       <c r="AK125" s="3"/>
       <c r="AL125" s="3"/>
     </row>
-    <row r="126" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A126" s="3"/>
       <c r="B126" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C126" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E126" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="D126" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="E126" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="F126" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G126" s="3"/>
       <c r="H126" s="3"/>
@@ -10044,19 +10044,19 @@
       <c r="AK126" s="3"/>
       <c r="AL126" s="3"/>
     </row>
-    <row r="127" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A127" s="3"/>
       <c r="B127" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D127" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>79</v>
@@ -10074,7 +10074,7 @@
         <v>47</v>
       </c>
       <c r="M127" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N127" s="3"/>
       <c r="O127" s="3"/>
@@ -10106,10 +10106,10 @@
       <c r="AC127" s="3"/>
       <c r="AD127" s="3"/>
       <c r="AE127" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF127" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG127" s="3">
         <v>1.4620299999999999</v>
@@ -10128,19 +10128,19 @@
       </c>
       <c r="AL127" s="3"/>
     </row>
-    <row r="128" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A128" s="3"/>
       <c r="B128" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C128" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E128" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="D128" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E128" s="3" t="s">
-        <v>134</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>79</v>
@@ -10158,7 +10158,7 @@
         <v>53</v>
       </c>
       <c r="M128" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N128" s="3"/>
       <c r="O128" s="3"/>
@@ -10190,10 +10190,10 @@
       <c r="AC128" s="3"/>
       <c r="AD128" s="3"/>
       <c r="AE128" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF128" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG128" s="3">
         <v>1.4620299999999999</v>
@@ -10212,19 +10212,19 @@
       </c>
       <c r="AL128" s="3"/>
     </row>
-    <row r="129" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A129" s="3"/>
       <c r="B129" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D129" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F129" s="3" t="s">
         <v>79</v>
@@ -10242,7 +10242,7 @@
         <v>47</v>
       </c>
       <c r="M129" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N129" s="3"/>
       <c r="O129" s="3"/>
@@ -10274,10 +10274,10 @@
       <c r="AC129" s="3"/>
       <c r="AD129" s="3"/>
       <c r="AE129" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF129" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG129" s="3">
         <v>1.4620299999999999</v>
@@ -10296,19 +10296,19 @@
       </c>
       <c r="AL129" s="3"/>
     </row>
-    <row r="130" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A130" s="3"/>
       <c r="B130" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C130" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E130" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="D130" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E130" s="3" t="s">
-        <v>134</v>
       </c>
       <c r="F130" s="3" t="s">
         <v>79</v>
@@ -10326,7 +10326,7 @@
         <v>53</v>
       </c>
       <c r="M130" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N130" s="3"/>
       <c r="O130" s="3"/>
@@ -10358,10 +10358,10 @@
       <c r="AC130" s="3"/>
       <c r="AD130" s="3"/>
       <c r="AE130" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF130" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG130" s="3">
         <v>1.4620299999999999</v>
@@ -10380,22 +10380,22 @@
       </c>
       <c r="AL130" s="3"/>
     </row>
-    <row r="131" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A131" s="3"/>
       <c r="B131" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D131" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G131" s="3"/>
       <c r="H131" s="3"/>
@@ -10448,22 +10448,22 @@
       <c r="AK131" s="3"/>
       <c r="AL131" s="3"/>
     </row>
-    <row r="132" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A132" s="3"/>
       <c r="B132" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D132" s="3" t="s">
         <v>73</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G132" s="3"/>
       <c r="H132" s="3"/>
@@ -10516,22 +10516,22 @@
       <c r="AK132" s="3"/>
       <c r="AL132" s="3"/>
     </row>
-    <row r="133" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A133" s="3"/>
       <c r="B133" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D133" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G133" s="3"/>
       <c r="H133" s="3" t="s">
@@ -10588,22 +10588,22 @@
       <c r="AK133" s="3"/>
       <c r="AL133" s="3"/>
     </row>
-    <row r="134" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A134" s="3"/>
       <c r="B134" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D134" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G134" s="3"/>
       <c r="H134" s="3" t="s">
@@ -10660,22 +10660,22 @@
       <c r="AK134" s="3"/>
       <c r="AL134" s="3"/>
     </row>
-    <row r="135" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A135" s="3"/>
       <c r="B135" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D135" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G135" s="3"/>
       <c r="H135" s="3" t="s">
@@ -10732,22 +10732,22 @@
       <c r="AK135" s="3"/>
       <c r="AL135" s="3"/>
     </row>
-    <row r="136" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A136" s="3"/>
       <c r="B136" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D136" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G136" s="3"/>
       <c r="H136" s="3" t="s">
@@ -10804,22 +10804,22 @@
       <c r="AK136" s="3"/>
       <c r="AL136" s="3"/>
     </row>
-    <row r="137" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A137" s="3"/>
       <c r="B137" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D137" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G137" s="3"/>
       <c r="H137" s="3"/>
@@ -10872,22 +10872,22 @@
       <c r="AK137" s="3"/>
       <c r="AL137" s="3"/>
     </row>
-    <row r="138" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A138" s="3"/>
       <c r="B138" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D138" s="3" t="s">
         <v>73</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G138" s="3"/>
       <c r="H138" s="3"/>
@@ -10940,22 +10940,22 @@
       <c r="AK138" s="3"/>
       <c r="AL138" s="3"/>
     </row>
-    <row r="139" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A139" s="3"/>
       <c r="B139" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C139" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E139" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D139" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="E139" s="3" t="s">
-        <v>136</v>
-      </c>
       <c r="F139" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G139" s="3"/>
       <c r="H139" s="3"/>
@@ -11008,22 +11008,22 @@
       <c r="AK139" s="3"/>
       <c r="AL139" s="3"/>
     </row>
-    <row r="140" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A140" s="3"/>
       <c r="B140" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D140" s="3" t="s">
         <v>73</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G140" s="3"/>
       <c r="H140" s="3"/>
@@ -11076,22 +11076,22 @@
       <c r="AK140" s="3"/>
       <c r="AL140" s="3"/>
     </row>
-    <row r="141" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A141" s="3"/>
       <c r="B141" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C141" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E141" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D141" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="E141" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="F141" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G141" s="3"/>
       <c r="H141" s="3"/>
@@ -11144,19 +11144,19 @@
       <c r="AK141" s="3"/>
       <c r="AL141" s="3"/>
     </row>
-    <row r="142" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A142" s="3"/>
       <c r="B142" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D142" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F142" s="3" t="s">
         <v>79</v>
@@ -11174,7 +11174,7 @@
         <v>47</v>
       </c>
       <c r="M142" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N142" s="3"/>
       <c r="O142" s="3"/>
@@ -11206,10 +11206,10 @@
       <c r="AC142" s="3"/>
       <c r="AD142" s="3"/>
       <c r="AE142" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF142" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AG142" s="3"/>
       <c r="AH142" s="3"/>
@@ -11224,19 +11224,19 @@
       </c>
       <c r="AL142" s="3"/>
     </row>
-    <row r="143" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A143" s="3"/>
       <c r="B143" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C143" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E143" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="D143" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E143" s="3" t="s">
-        <v>140</v>
       </c>
       <c r="F143" s="3" t="s">
         <v>79</v>
@@ -11254,7 +11254,7 @@
         <v>53</v>
       </c>
       <c r="M143" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N143" s="3"/>
       <c r="O143" s="3"/>
@@ -11286,10 +11286,10 @@
       <c r="AC143" s="3"/>
       <c r="AD143" s="3"/>
       <c r="AE143" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF143" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AG143" s="3"/>
       <c r="AH143" s="3"/>
@@ -11304,19 +11304,19 @@
       </c>
       <c r="AL143" s="3"/>
     </row>
-    <row r="144" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A144" s="3"/>
       <c r="B144" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D144" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F144" s="3" t="s">
         <v>79</v>
@@ -11334,7 +11334,7 @@
         <v>47</v>
       </c>
       <c r="M144" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N144" s="3"/>
       <c r="O144" s="3"/>
@@ -11366,10 +11366,10 @@
       <c r="AC144" s="3"/>
       <c r="AD144" s="3"/>
       <c r="AE144" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF144" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AG144" s="3"/>
       <c r="AH144" s="3"/>
@@ -11384,19 +11384,19 @@
       </c>
       <c r="AL144" s="3"/>
     </row>
-    <row r="145" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A145" s="3"/>
       <c r="B145" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C145" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E145" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="D145" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E145" s="3" t="s">
-        <v>140</v>
       </c>
       <c r="F145" s="3" t="s">
         <v>79</v>
@@ -11414,7 +11414,7 @@
         <v>53</v>
       </c>
       <c r="M145" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N145" s="3"/>
       <c r="O145" s="3"/>
@@ -11446,10 +11446,10 @@
       <c r="AC145" s="3"/>
       <c r="AD145" s="3"/>
       <c r="AE145" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF145" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AG145" s="3"/>
       <c r="AH145" s="3"/>
@@ -11464,22 +11464,22 @@
       </c>
       <c r="AL145" s="3"/>
     </row>
-    <row r="146" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A146" s="3"/>
       <c r="B146" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D146" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G146" s="3"/>
       <c r="H146" s="3"/>
@@ -11532,22 +11532,22 @@
       <c r="AK146" s="3"/>
       <c r="AL146" s="3"/>
     </row>
-    <row r="147" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A147" s="3"/>
       <c r="B147" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D147" s="3" t="s">
         <v>73</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G147" s="3"/>
       <c r="H147" s="3"/>
@@ -11600,22 +11600,22 @@
       <c r="AK147" s="3"/>
       <c r="AL147" s="3"/>
     </row>
-    <row r="148" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A148" s="3"/>
       <c r="B148" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C148" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E148" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D148" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="E148" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="F148" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G148" s="3"/>
       <c r="H148" s="3"/>
@@ -11668,22 +11668,22 @@
       <c r="AK148" s="3"/>
       <c r="AL148" s="3"/>
     </row>
-    <row r="149" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A149" s="3"/>
       <c r="B149" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D149" s="3" t="s">
         <v>73</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G149" s="3"/>
       <c r="H149" s="3"/>

--- a/inst/extdata/ute_mountain_ute_tribe_criteria_crosswalk.xlsx
+++ b/inst/extdata/ute_mountain_ute_tribe_criteria_crosswalk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/hannah_ferriby_tetratech_com/Documents/Documents/GitHub/TADACommunityHub/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="13_ncr:1_{D17CFB82-D889-430F-8BAD-637D486FCCA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACBCB4FA-62A9-43FF-899D-0DEF14C60D75}"/>
+  <xr:revisionPtr revIDLastSave="73" documentId="13_ncr:1_{D17CFB82-D889-430F-8BAD-637D486FCCA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C379A56-048E-4CF4-BCCE-B888FD457509}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0939A520-3B6D-499A-B5C0-4CEBC761A507}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{0939A520-3B6D-499A-B5C0-4CEBC761A507}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1888" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1891" uniqueCount="179">
   <si>
     <t>TADA.ComparableDataIdentifier</t>
   </si>
@@ -533,9 +533,6 @@
     <t>pHDirection</t>
   </si>
   <si>
-    <t>TemperatureExtreme</t>
-  </si>
-  <si>
     <t>MinEqMagnitued</t>
   </si>
   <si>
@@ -560,10 +557,22 @@
     <t>((0.0577/(1+10^(7.688-pH))) + (2.487/(1+10^(pH-7.688)))) * 1.45*10^(0.028*(25-max(Temperature,7)))</t>
   </si>
   <si>
-    <t>Max</t>
-  </si>
-  <si>
-    <t>Min</t>
+    <t>AmmoniaEqType</t>
+  </si>
+  <si>
+    <t>Max Exponent</t>
+  </si>
+  <si>
+    <t>Min Multiplier</t>
+  </si>
+  <si>
+    <t>pH_param_10</t>
+  </si>
+  <si>
+    <t>pH_param_11</t>
+  </si>
+  <si>
+    <t>pH_param_12</t>
   </si>
 </sst>
 </file>
@@ -969,21 +978,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5669769F-2254-4C2D-A5BA-32D6C5B999AC}">
-  <dimension ref="A1:AX149"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:BA149"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="5"/>
-    <col min="2" max="2" width="29.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="31" width="9.140625" style="5"/>
-    <col min="32" max="32" width="102.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="19.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="10.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="5"/>
+    <col min="1" max="1" width="9.109375" style="5"/>
+    <col min="2" max="2" width="29.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="31" width="9.109375" style="5"/>
+    <col min="32" max="32" width="102.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="19.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="10.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.109375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:53" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1099,7 +1108,7 @@
         <v>34</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="AN1" s="1" t="s">
         <v>35</v>
@@ -1114,28 +1123,37 @@
         <v>38</v>
       </c>
       <c r="AR1" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="AS1" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="AV1" s="1" t="s">
-        <v>172</v>
-      </c>
       <c r="AW1" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="BA1" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="AX1" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="2" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
         <v>39</v>
@@ -1206,7 +1224,7 @@
       <c r="AL2" s="3"/>
       <c r="AM2" s="3"/>
     </row>
-    <row r="3" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
         <v>39</v>
@@ -1277,7 +1295,7 @@
       <c r="AL3" s="3"/>
       <c r="AM3" s="3"/>
     </row>
-    <row r="4" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
         <v>39</v>
@@ -1346,7 +1364,7 @@
       <c r="AL4" s="3"/>
       <c r="AM4" s="3"/>
     </row>
-    <row r="5" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
         <v>39</v>
@@ -1415,7 +1433,7 @@
       <c r="AL5" s="3"/>
       <c r="AM5" s="3"/>
     </row>
-    <row r="6" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
         <v>39</v>
@@ -1484,7 +1502,7 @@
       <c r="AL6" s="3"/>
       <c r="AM6" s="3"/>
     </row>
-    <row r="7" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
         <v>39</v>
@@ -1553,7 +1571,7 @@
       <c r="AL7" s="3"/>
       <c r="AM7" s="3"/>
     </row>
-    <row r="8" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
         <v>39</v>
@@ -1622,7 +1640,7 @@
       <c r="AL8" s="3"/>
       <c r="AM8" s="3"/>
     </row>
-    <row r="9" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
         <v>39</v>
@@ -1693,7 +1711,7 @@
       <c r="AL9" s="3"/>
       <c r="AM9" s="3"/>
     </row>
-    <row r="10" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
         <v>39</v>
@@ -1762,7 +1780,7 @@
       <c r="AL10" s="3"/>
       <c r="AM10" s="3"/>
     </row>
-    <row r="11" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
         <v>39</v>
@@ -1831,7 +1849,7 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
         <v>39</v>
@@ -1900,7 +1918,7 @@
       <c r="AL12" s="3"/>
       <c r="AM12" s="3"/>
     </row>
-    <row r="13" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
         <v>39</v>
@@ -1969,7 +1987,7 @@
       <c r="AL13" s="3"/>
       <c r="AM13" s="3"/>
     </row>
-    <row r="14" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
         <v>39</v>
@@ -2038,7 +2056,7 @@
       <c r="AL14" s="3"/>
       <c r="AM14" s="3"/>
     </row>
-    <row r="15" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
         <v>39</v>
@@ -2107,7 +2125,7 @@
       <c r="AL15" s="3"/>
       <c r="AM15" s="3"/>
     </row>
-    <row r="16" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
         <v>39</v>
@@ -2176,7 +2194,7 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
         <v>39</v>
@@ -2245,7 +2263,7 @@
       <c r="AL17" s="3"/>
       <c r="AM17" s="3"/>
     </row>
-    <row r="18" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
         <v>39</v>
@@ -2314,7 +2332,7 @@
       <c r="AL18" s="3"/>
       <c r="AM18" s="3"/>
     </row>
-    <row r="19" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
         <v>39</v>
@@ -2383,7 +2401,7 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
         <v>39</v>
@@ -2454,7 +2472,7 @@
       <c r="AL20" s="3"/>
       <c r="AM20" s="3"/>
     </row>
-    <row r="21" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
         <v>39</v>
@@ -2525,7 +2543,7 @@
       <c r="AL21" s="3"/>
       <c r="AM21" s="3"/>
     </row>
-    <row r="22" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
         <v>39</v>
@@ -2596,7 +2614,7 @@
       <c r="AL22" s="3"/>
       <c r="AM22" s="3"/>
     </row>
-    <row r="23" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
         <v>39</v>
@@ -2667,7 +2685,7 @@
       <c r="AL23" s="3"/>
       <c r="AM23" s="3"/>
     </row>
-    <row r="24" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
         <v>39</v>
@@ -2738,7 +2756,7 @@
       <c r="AL24" s="3"/>
       <c r="AM24" s="3"/>
     </row>
-    <row r="25" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
         <v>39</v>
@@ -2809,7 +2827,7 @@
       <c r="AL25" s="3"/>
       <c r="AM25" s="3"/>
     </row>
-    <row r="26" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
         <v>39</v>
@@ -2880,7 +2898,7 @@
       <c r="AL26" s="3"/>
       <c r="AM26" s="3"/>
     </row>
-    <row r="27" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
         <v>39</v>
@@ -2951,7 +2969,7 @@
       <c r="AL27" s="3"/>
       <c r="AM27" s="3"/>
     </row>
-    <row r="28" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
         <v>39</v>
@@ -3022,7 +3040,7 @@
       <c r="AL28" s="3"/>
       <c r="AM28" s="3"/>
     </row>
-    <row r="29" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
         <v>39</v>
@@ -3093,7 +3111,7 @@
       <c r="AL29" s="3"/>
       <c r="AM29" s="3"/>
     </row>
-    <row r="30" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
         <v>39</v>
@@ -3160,7 +3178,7 @@
       <c r="AL30" s="3"/>
       <c r="AM30" s="3"/>
     </row>
-    <row r="31" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
         <v>39</v>
@@ -3227,7 +3245,7 @@
       <c r="AL31" s="3"/>
       <c r="AM31" s="3"/>
     </row>
-    <row r="32" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
         <v>39</v>
@@ -3294,7 +3312,7 @@
       <c r="AL32" s="3"/>
       <c r="AM32" s="3"/>
     </row>
-    <row r="33" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
         <v>39</v>
@@ -3379,7 +3397,7 @@
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="34" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
         <v>39</v>
@@ -3464,7 +3482,7 @@
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="35" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
         <v>39</v>
@@ -3527,7 +3545,7 @@
         <v>89</v>
       </c>
       <c r="AF35" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG35" s="3"/>
       <c r="AH35" s="3"/>
@@ -3566,7 +3584,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
         <v>39</v>
@@ -3629,7 +3647,7 @@
         <v>89</v>
       </c>
       <c r="AF36" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG36" s="3"/>
       <c r="AH36" s="3"/>
@@ -3668,7 +3686,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
         <v>39</v>
@@ -3753,7 +3771,7 @@
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
         <v>39</v>
@@ -3838,7 +3856,7 @@
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
         <v>39</v>
@@ -3940,7 +3958,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="3"/>
       <c r="B40" s="3" t="s">
         <v>39</v>
@@ -4042,7 +4060,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="3"/>
       <c r="B41" s="3" t="s">
         <v>39</v>
@@ -4111,7 +4129,7 @@
       <c r="AL41" s="3"/>
       <c r="AM41" s="3"/>
     </row>
-    <row r="42" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="3"/>
       <c r="B42" s="3" t="s">
         <v>39</v>
@@ -4184,7 +4202,7 @@
       <c r="AL42" s="3"/>
       <c r="AM42" s="3"/>
     </row>
-    <row r="43" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
         <v>39</v>
@@ -4257,7 +4275,7 @@
       <c r="AL43" s="3"/>
       <c r="AM43" s="3"/>
     </row>
-    <row r="44" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
         <v>39</v>
@@ -4330,7 +4348,7 @@
       <c r="AL44" s="3"/>
       <c r="AM44" s="3"/>
     </row>
-    <row r="45" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="3"/>
       <c r="B45" s="3" t="s">
         <v>39</v>
@@ -4403,7 +4421,7 @@
       <c r="AL45" s="3"/>
       <c r="AM45" s="3"/>
     </row>
-    <row r="46" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="3"/>
       <c r="B46" s="3" t="s">
         <v>39</v>
@@ -4474,7 +4492,7 @@
       <c r="AL46" s="3"/>
       <c r="AM46" s="3"/>
     </row>
-    <row r="47" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="3"/>
       <c r="B47" s="3" t="s">
         <v>39</v>
@@ -4547,7 +4565,7 @@
       <c r="AL47" s="3"/>
       <c r="AM47" s="3"/>
     </row>
-    <row r="48" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
       <c r="B48" s="3" t="s">
         <v>39</v>
@@ -4620,7 +4638,7 @@
       <c r="AL48" s="3"/>
       <c r="AM48" s="3"/>
     </row>
-    <row r="49" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
       <c r="B49" s="3" t="s">
         <v>39</v>
@@ -4693,7 +4711,7 @@
       <c r="AL49" s="3"/>
       <c r="AM49" s="3"/>
     </row>
-    <row r="50" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="3"/>
       <c r="B50" s="3" t="s">
         <v>39</v>
@@ -4766,7 +4784,7 @@
       <c r="AL50" s="3"/>
       <c r="AM50" s="3"/>
     </row>
-    <row r="51" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="3"/>
       <c r="B51" s="3" t="s">
         <v>39</v>
@@ -4835,7 +4853,7 @@
       <c r="AL51" s="3"/>
       <c r="AM51" s="3"/>
     </row>
-    <row r="52" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="3"/>
       <c r="B52" s="3" t="s">
         <v>39</v>
@@ -4904,7 +4922,7 @@
       <c r="AL52" s="3"/>
       <c r="AM52" s="3"/>
     </row>
-    <row r="53" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="3"/>
       <c r="B53" s="3" t="s">
         <v>39</v>
@@ -4973,7 +4991,7 @@
       <c r="AL53" s="3"/>
       <c r="AM53" s="3"/>
     </row>
-    <row r="54" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="3"/>
       <c r="B54" s="3" t="s">
         <v>39</v>
@@ -5042,7 +5060,7 @@
       <c r="AL54" s="3"/>
       <c r="AM54" s="3"/>
     </row>
-    <row r="55" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="3"/>
       <c r="B55" s="3" t="s">
         <v>39</v>
@@ -5113,7 +5131,7 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="3"/>
       <c r="B56" s="3" t="s">
         <v>39</v>
@@ -5184,7 +5202,7 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="3"/>
       <c r="B57" s="3" t="s">
         <v>39</v>
@@ -5255,7 +5273,7 @@
       <c r="AL57" s="3"/>
       <c r="AM57" s="3"/>
     </row>
-    <row r="58" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="3"/>
       <c r="B58" s="3" t="s">
         <v>39</v>
@@ -5326,7 +5344,7 @@
       <c r="AL58" s="3"/>
       <c r="AM58" s="3"/>
     </row>
-    <row r="59" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="3"/>
       <c r="B59" s="3" t="s">
         <v>39</v>
@@ -5395,7 +5413,7 @@
       <c r="AL59" s="3"/>
       <c r="AM59" s="3"/>
     </row>
-    <row r="60" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="3"/>
       <c r="B60" s="3" t="s">
         <v>39</v>
@@ -5464,7 +5482,7 @@
       <c r="AL60" s="3"/>
       <c r="AM60" s="3"/>
     </row>
-    <row r="61" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="3"/>
       <c r="B61" s="3" t="s">
         <v>39</v>
@@ -5533,7 +5551,7 @@
       <c r="AL61" s="3"/>
       <c r="AM61" s="3"/>
     </row>
-    <row r="62" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A62" s="3"/>
       <c r="B62" s="3" t="s">
         <v>39</v>
@@ -5604,7 +5622,7 @@
       <c r="AL62" s="3"/>
       <c r="AM62" s="3"/>
     </row>
-    <row r="63" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="3"/>
       <c r="B63" s="3" t="s">
         <v>39</v>
@@ -5675,7 +5693,7 @@
       <c r="AL63" s="3"/>
       <c r="AM63" s="3"/>
     </row>
-    <row r="64" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="3"/>
       <c r="B64" s="3" t="s">
         <v>39</v>
@@ -5744,7 +5762,7 @@
       <c r="AL64" s="3"/>
       <c r="AM64" s="3"/>
     </row>
-    <row r="65" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A65" s="3"/>
       <c r="B65" s="3" t="s">
         <v>39</v>
@@ -5813,7 +5831,7 @@
       <c r="AL65" s="3"/>
       <c r="AM65" s="3"/>
     </row>
-    <row r="66" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A66" s="3"/>
       <c r="B66" s="3" t="s">
         <v>39</v>
@@ -5893,7 +5911,7 @@
         <v>-6.52</v>
       </c>
     </row>
-    <row r="67" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A67" s="3"/>
       <c r="B67" s="3" t="s">
         <v>39</v>
@@ -5973,7 +5991,7 @@
         <v>-6.52</v>
       </c>
     </row>
-    <row r="68" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A68" s="3"/>
       <c r="B68" s="3" t="s">
         <v>39</v>
@@ -6053,7 +6071,7 @@
         <v>-9.06</v>
       </c>
     </row>
-    <row r="69" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A69" s="3"/>
       <c r="B69" s="3" t="s">
         <v>39</v>
@@ -6133,7 +6151,7 @@
         <v>-10.51</v>
       </c>
     </row>
-    <row r="70" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A70" s="3"/>
       <c r="B70" s="3" t="s">
         <v>39</v>
@@ -6202,7 +6220,7 @@
       <c r="AL70" s="3"/>
       <c r="AM70" s="3"/>
     </row>
-    <row r="71" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A71" s="3"/>
       <c r="B71" s="3" t="s">
         <v>39</v>
@@ -6271,7 +6289,7 @@
       <c r="AL71" s="3"/>
       <c r="AM71" s="3"/>
     </row>
-    <row r="72" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A72" s="3"/>
       <c r="B72" s="3" t="s">
         <v>39</v>
@@ -6344,7 +6362,7 @@
       <c r="AL72" s="3"/>
       <c r="AM72" s="3"/>
     </row>
-    <row r="73" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A73" s="3"/>
       <c r="B73" s="3" t="s">
         <v>39</v>
@@ -6417,7 +6435,7 @@
       <c r="AL73" s="3"/>
       <c r="AM73" s="3"/>
     </row>
-    <row r="74" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A74" s="3"/>
       <c r="B74" s="3" t="s">
         <v>39</v>
@@ -6490,7 +6508,7 @@
       <c r="AL74" s="3"/>
       <c r="AM74" s="3"/>
     </row>
-    <row r="75" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A75" s="3"/>
       <c r="B75" s="3" t="s">
         <v>39</v>
@@ -6563,7 +6581,7 @@
       <c r="AL75" s="3"/>
       <c r="AM75" s="3"/>
     </row>
-    <row r="76" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A76" s="3"/>
       <c r="B76" s="3" t="s">
         <v>39</v>
@@ -6632,7 +6650,7 @@
       <c r="AL76" s="3"/>
       <c r="AM76" s="3"/>
     </row>
-    <row r="77" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A77" s="3"/>
       <c r="B77" s="3" t="s">
         <v>39</v>
@@ -6703,7 +6721,7 @@
       <c r="AL77" s="3"/>
       <c r="AM77" s="3"/>
     </row>
-    <row r="78" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A78" s="3"/>
       <c r="B78" s="3" t="s">
         <v>39</v>
@@ -6776,7 +6794,7 @@
       <c r="AL78" s="3"/>
       <c r="AM78" s="3"/>
     </row>
-    <row r="79" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A79" s="3"/>
       <c r="B79" s="3" t="s">
         <v>39</v>
@@ -6849,7 +6867,7 @@
       <c r="AL79" s="3"/>
       <c r="AM79" s="3"/>
     </row>
-    <row r="80" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A80" s="3"/>
       <c r="B80" s="3" t="s">
         <v>39</v>
@@ -6922,7 +6940,7 @@
       <c r="AL80" s="3"/>
       <c r="AM80" s="3"/>
     </row>
-    <row r="81" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A81" s="3"/>
       <c r="B81" s="3" t="s">
         <v>39</v>
@@ -6991,7 +7009,7 @@
       <c r="AL81" s="3"/>
       <c r="AM81" s="3"/>
     </row>
-    <row r="82" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A82" s="3"/>
       <c r="B82" s="3" t="s">
         <v>39</v>
@@ -7060,7 +7078,7 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A83" s="3"/>
       <c r="B83" s="3" t="s">
         <v>39</v>
@@ -7129,7 +7147,7 @@
       <c r="AL83" s="3"/>
       <c r="AM83" s="3"/>
     </row>
-    <row r="84" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A84" s="3"/>
       <c r="B84" s="3" t="s">
         <v>39</v>
@@ -7200,7 +7218,7 @@
       <c r="AL84" s="3"/>
       <c r="AM84" s="3"/>
     </row>
-    <row r="85" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A85" s="3"/>
       <c r="B85" s="3" t="s">
         <v>39</v>
@@ -7282,7 +7300,7 @@
         <v>-3.9239999999999999</v>
       </c>
     </row>
-    <row r="86" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A86" s="3"/>
       <c r="B86" s="3" t="s">
         <v>39</v>
@@ -7364,7 +7382,7 @@
         <v>-3.9239999999999999</v>
       </c>
     </row>
-    <row r="87" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A87" s="3"/>
       <c r="B87" s="3" t="s">
         <v>39</v>
@@ -7446,7 +7464,7 @@
         <v>-4.7190000000000003</v>
       </c>
     </row>
-    <row r="88" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A88" s="3"/>
       <c r="B88" s="3" t="s">
         <v>39</v>
@@ -7528,7 +7546,7 @@
         <v>-4.7190000000000003</v>
       </c>
     </row>
-    <row r="89" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A89" s="3"/>
       <c r="B89" s="3" t="s">
         <v>39</v>
@@ -7597,7 +7615,7 @@
       <c r="AL89" s="3"/>
       <c r="AM89" s="3"/>
     </row>
-    <row r="90" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A90" s="3"/>
       <c r="B90" s="3" t="s">
         <v>39</v>
@@ -7666,7 +7684,7 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A91" s="3"/>
       <c r="B91" s="3" t="s">
         <v>39</v>
@@ -7735,7 +7753,7 @@
       <c r="AL91" s="3"/>
       <c r="AM91" s="3"/>
     </row>
-    <row r="92" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A92" s="3"/>
       <c r="B92" s="3" t="s">
         <v>39</v>
@@ -7815,7 +7833,7 @@
         <v>3.7256</v>
       </c>
     </row>
-    <row r="93" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A93" s="3"/>
       <c r="B93" s="3" t="s">
         <v>39</v>
@@ -7895,7 +7913,7 @@
         <v>3.7256</v>
       </c>
     </row>
-    <row r="94" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A94" s="3"/>
       <c r="B94" s="3" t="s">
         <v>39</v>
@@ -7975,7 +7993,7 @@
         <v>0.68479999999999996</v>
       </c>
     </row>
-    <row r="95" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A95" s="3"/>
       <c r="B95" s="3" t="s">
         <v>39</v>
@@ -8055,7 +8073,7 @@
         <v>0.68479999999999996</v>
       </c>
     </row>
-    <row r="96" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A96" s="3"/>
       <c r="B96" s="3" t="s">
         <v>39</v>
@@ -8124,7 +8142,7 @@
       <c r="AL96" s="3"/>
       <c r="AM96" s="3"/>
     </row>
-    <row r="97" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A97" s="3"/>
       <c r="B97" s="3" t="s">
         <v>39</v>
@@ -8193,7 +8211,7 @@
       <c r="AL97" s="3"/>
       <c r="AM97" s="3"/>
     </row>
-    <row r="98" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A98" s="3"/>
       <c r="B98" s="3" t="s">
         <v>39</v>
@@ -8262,7 +8280,7 @@
       <c r="AL98" s="3"/>
       <c r="AM98" s="3"/>
     </row>
-    <row r="99" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A99" s="3"/>
       <c r="B99" s="3" t="s">
         <v>39</v>
@@ -8335,7 +8353,7 @@
       <c r="AL99" s="3"/>
       <c r="AM99" s="3"/>
     </row>
-    <row r="100" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A100" s="3"/>
       <c r="B100" s="3" t="s">
         <v>39</v>
@@ -8408,7 +8426,7 @@
       <c r="AL100" s="3"/>
       <c r="AM100" s="3"/>
     </row>
-    <row r="101" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A101" s="3"/>
       <c r="B101" s="3" t="s">
         <v>39</v>
@@ -8481,7 +8499,7 @@
       <c r="AL101" s="3"/>
       <c r="AM101" s="3"/>
     </row>
-    <row r="102" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A102" s="3"/>
       <c r="B102" s="3" t="s">
         <v>39</v>
@@ -8554,7 +8572,7 @@
       <c r="AL102" s="3"/>
       <c r="AM102" s="3"/>
     </row>
-    <row r="103" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A103" s="3"/>
       <c r="B103" s="3" t="s">
         <v>39</v>
@@ -8623,7 +8641,7 @@
       <c r="AL103" s="3"/>
       <c r="AM103" s="3"/>
     </row>
-    <row r="104" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A104" s="3"/>
       <c r="B104" s="3" t="s">
         <v>39</v>
@@ -8692,7 +8710,7 @@
       <c r="AL104" s="3"/>
       <c r="AM104" s="3"/>
     </row>
-    <row r="105" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A105" s="3"/>
       <c r="B105" s="3" t="s">
         <v>39</v>
@@ -8761,7 +8779,7 @@
       <c r="AL105" s="3"/>
       <c r="AM105" s="3"/>
     </row>
-    <row r="106" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A106" s="3"/>
       <c r="B106" s="3" t="s">
         <v>39</v>
@@ -8841,7 +8859,7 @@
         <v>-1.7</v>
       </c>
     </row>
-    <row r="107" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A107" s="3"/>
       <c r="B107" s="3" t="s">
         <v>39</v>
@@ -8921,7 +8939,7 @@
         <v>-1.7</v>
       </c>
     </row>
-    <row r="108" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A108" s="3"/>
       <c r="B108" s="3" t="s">
         <v>39</v>
@@ -9001,7 +9019,7 @@
         <v>-1.702</v>
       </c>
     </row>
-    <row r="109" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A109" s="3"/>
       <c r="B109" s="3" t="s">
         <v>39</v>
@@ -9081,7 +9099,7 @@
         <v>-1.702</v>
       </c>
     </row>
-    <row r="110" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A110" s="3"/>
       <c r="B110" s="3" t="s">
         <v>39</v>
@@ -9150,7 +9168,7 @@
       <c r="AL110" s="3"/>
       <c r="AM110" s="3"/>
     </row>
-    <row r="111" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A111" s="3"/>
       <c r="B111" s="3" t="s">
         <v>39</v>
@@ -9219,7 +9237,7 @@
       <c r="AL111" s="3"/>
       <c r="AM111" s="3"/>
     </row>
-    <row r="112" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A112" s="3"/>
       <c r="B112" s="3" t="s">
         <v>39</v>
@@ -9292,7 +9310,7 @@
       <c r="AL112" s="3"/>
       <c r="AM112" s="3"/>
     </row>
-    <row r="113" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A113" s="3"/>
       <c r="B113" s="3" t="s">
         <v>39</v>
@@ -9365,7 +9383,7 @@
       <c r="AL113" s="3"/>
       <c r="AM113" s="3"/>
     </row>
-    <row r="114" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A114" s="3"/>
       <c r="B114" s="3" t="s">
         <v>39</v>
@@ -9438,7 +9456,7 @@
       <c r="AL114" s="3"/>
       <c r="AM114" s="3"/>
     </row>
-    <row r="115" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A115" s="3"/>
       <c r="B115" s="3" t="s">
         <v>39</v>
@@ -9511,7 +9529,7 @@
       <c r="AL115" s="3"/>
       <c r="AM115" s="3"/>
     </row>
-    <row r="116" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A116" s="3"/>
       <c r="B116" s="3" t="s">
         <v>39</v>
@@ -9580,7 +9598,7 @@
       <c r="AL116" s="3"/>
       <c r="AM116" s="3"/>
     </row>
-    <row r="117" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A117" s="3"/>
       <c r="B117" s="3" t="s">
         <v>39</v>
@@ -9649,7 +9667,7 @@
       <c r="AL117" s="3"/>
       <c r="AM117" s="3"/>
     </row>
-    <row r="118" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A118" s="3"/>
       <c r="B118" s="3" t="s">
         <v>39</v>
@@ -9718,7 +9736,7 @@
       <c r="AL118" s="3"/>
       <c r="AM118" s="3"/>
     </row>
-    <row r="119" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A119" s="3"/>
       <c r="B119" s="3" t="s">
         <v>39</v>
@@ -9787,7 +9805,7 @@
       <c r="AL119" s="3"/>
       <c r="AM119" s="3"/>
     </row>
-    <row r="120" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A120" s="3"/>
       <c r="B120" s="3" t="s">
         <v>39</v>
@@ -9867,7 +9885,7 @@
         <v>2.2549999999999999</v>
       </c>
     </row>
-    <row r="121" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A121" s="3"/>
       <c r="B121" s="3" t="s">
         <v>39</v>
@@ -9947,7 +9965,7 @@
         <v>2.2549999999999999</v>
       </c>
     </row>
-    <row r="122" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A122" s="3"/>
       <c r="B122" s="3" t="s">
         <v>39</v>
@@ -10027,7 +10045,7 @@
         <v>5.8400000000000001E-2</v>
       </c>
     </row>
-    <row r="123" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A123" s="3"/>
       <c r="B123" s="3" t="s">
         <v>39</v>
@@ -10107,7 +10125,7 @@
         <v>5.8400000000000001E-2</v>
       </c>
     </row>
-    <row r="124" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A124" s="3"/>
       <c r="B124" s="3" t="s">
         <v>39</v>
@@ -10176,7 +10194,7 @@
       <c r="AL124" s="3"/>
       <c r="AM124" s="3"/>
     </row>
-    <row r="125" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A125" s="3"/>
       <c r="B125" s="3" t="s">
         <v>39</v>
@@ -10245,7 +10263,7 @@
       <c r="AL125" s="3"/>
       <c r="AM125" s="3"/>
     </row>
-    <row r="126" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A126" s="3"/>
       <c r="B126" s="3" t="s">
         <v>39</v>
@@ -10314,7 +10332,7 @@
       <c r="AL126" s="3"/>
       <c r="AM126" s="3"/>
     </row>
-    <row r="127" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A127" s="3"/>
       <c r="B127" s="3" t="s">
         <v>39</v>
@@ -10396,7 +10414,7 @@
         <v>-1.46</v>
       </c>
     </row>
-    <row r="128" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A128" s="3"/>
       <c r="B128" s="3" t="s">
         <v>39</v>
@@ -10478,7 +10496,7 @@
         <v>-1.46</v>
       </c>
     </row>
-    <row r="129" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A129" s="3"/>
       <c r="B129" s="3" t="s">
         <v>39</v>
@@ -10560,7 +10578,7 @@
         <v>-1.46</v>
       </c>
     </row>
-    <row r="130" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A130" s="3"/>
       <c r="B130" s="3" t="s">
         <v>39</v>
@@ -10642,7 +10660,7 @@
         <v>-1.46</v>
       </c>
     </row>
-    <row r="131" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A131" s="3"/>
       <c r="B131" s="3" t="s">
         <v>39</v>
@@ -10711,7 +10729,7 @@
       <c r="AL131" s="3"/>
       <c r="AM131" s="3"/>
     </row>
-    <row r="132" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A132" s="3"/>
       <c r="B132" s="3" t="s">
         <v>39</v>
@@ -10780,7 +10798,7 @@
       <c r="AL132" s="3"/>
       <c r="AM132" s="3"/>
     </row>
-    <row r="133" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A133" s="3"/>
       <c r="B133" s="3" t="s">
         <v>39</v>
@@ -10853,7 +10871,7 @@
       <c r="AL133" s="3"/>
       <c r="AM133" s="3"/>
     </row>
-    <row r="134" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A134" s="3"/>
       <c r="B134" s="3" t="s">
         <v>39</v>
@@ -10926,7 +10944,7 @@
       <c r="AL134" s="3"/>
       <c r="AM134" s="3"/>
     </row>
-    <row r="135" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A135" s="3"/>
       <c r="B135" s="3" t="s">
         <v>39</v>
@@ -10999,7 +11017,7 @@
       <c r="AL135" s="3"/>
       <c r="AM135" s="3"/>
     </row>
-    <row r="136" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A136" s="3"/>
       <c r="B136" s="3" t="s">
         <v>39</v>
@@ -11072,7 +11090,7 @@
       <c r="AL136" s="3"/>
       <c r="AM136" s="3"/>
     </row>
-    <row r="137" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A137" s="3"/>
       <c r="B137" s="3" t="s">
         <v>39</v>
@@ -11141,7 +11159,7 @@
       <c r="AL137" s="3"/>
       <c r="AM137" s="3"/>
     </row>
-    <row r="138" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A138" s="3"/>
       <c r="B138" s="3" t="s">
         <v>39</v>
@@ -11210,7 +11228,7 @@
       <c r="AL138" s="3"/>
       <c r="AM138" s="3"/>
     </row>
-    <row r="139" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A139" s="3"/>
       <c r="B139" s="3" t="s">
         <v>39</v>
@@ -11279,7 +11297,7 @@
       <c r="AL139" s="3"/>
       <c r="AM139" s="3"/>
     </row>
-    <row r="140" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A140" s="3"/>
       <c r="B140" s="3" t="s">
         <v>39</v>
@@ -11348,7 +11366,7 @@
       <c r="AL140" s="3"/>
       <c r="AM140" s="3"/>
     </row>
-    <row r="141" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A141" s="3"/>
       <c r="B141" s="3" t="s">
         <v>39</v>
@@ -11417,7 +11435,7 @@
       <c r="AL141" s="3"/>
       <c r="AM141" s="3"/>
     </row>
-    <row r="142" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A142" s="3"/>
       <c r="B142" s="3" t="s">
         <v>39</v>
@@ -11497,7 +11515,7 @@
         <v>0.88400000000000001</v>
       </c>
     </row>
-    <row r="143" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A143" s="3"/>
       <c r="B143" s="3" t="s">
         <v>39</v>
@@ -11577,7 +11595,7 @@
         <v>0.88400000000000001</v>
       </c>
     </row>
-    <row r="144" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A144" s="3"/>
       <c r="B144" s="3" t="s">
         <v>39</v>
@@ -11657,7 +11675,7 @@
         <v>0.88400000000000001</v>
       </c>
     </row>
-    <row r="145" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A145" s="3"/>
       <c r="B145" s="3" t="s">
         <v>39</v>
@@ -11737,7 +11755,7 @@
         <v>0.88400000000000001</v>
       </c>
     </row>
-    <row r="146" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A146" s="3"/>
       <c r="B146" s="3" t="s">
         <v>39</v>
@@ -11806,7 +11824,7 @@
       <c r="AL146" s="3"/>
       <c r="AM146" s="3"/>
     </row>
-    <row r="147" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A147" s="3"/>
       <c r="B147" s="3" t="s">
         <v>39</v>
@@ -11875,7 +11893,7 @@
       <c r="AL147" s="3"/>
       <c r="AM147" s="3"/>
     </row>
-    <row r="148" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A148" s="3"/>
       <c r="B148" s="3" t="s">
         <v>39</v>
@@ -11944,7 +11962,7 @@
       <c r="AL148" s="3"/>
       <c r="AM148" s="3"/>
     </row>
-    <row r="149" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A149" s="3"/>
       <c r="B149" s="3" t="s">
         <v>39</v>
